--- a/data/lng_sentiment_score_.xlsx
+++ b/data/lng_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6706,6 +6706,1895 @@
         <v>0.6369</v>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/poland-offers-help-ukraine-reels-114445434.html</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2025-10-10T11:44:45Z</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Poland offers help as Ukraine reels from Russian attacks on energy infrastructure</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>WARSAW (Reuters) -Generators, extra electricity supplies and an LNG terminal are at Ukraine's disposal, Polish foreign minister Radoslaw Sikorski said on...</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>WARSAW (Reuters) -Generators, extra electricity supplies and an LNG terminal are at Ukraine's disposal, Polish foreign minister Radoslaw Sikorski said on Friday, as Russia continues to attack Kyiv's … [+1131 chars]</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>-0.4648</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/gold-set-become-australias-second-220826882.html</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2025-10-06T22:08:26Z</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Gold set to become Australia's second-biggest resource earner</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>MELBOURNE (Reuters) -Australia said on Tuesday it expected gold to become its second most valuable resource export after iron ore this financial year...</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>MELBOURNE (Reuters) -Australia said on Tuesday it expected gold to become its second most valuable resource export after iron ore this financial year, dislodging liquefied natural gas, as concerns ov… [+2096 chars]</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>0.7089</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/goldman-sachs-initiates-coverage-golar-111646164.html</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Faheem Tahir</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2025-10-15T11:16:46Z</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Goldman Sachs Initiates Coverage of Golar LNG Limited (GLNG) with “Buy” Rating and $54 PT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>RIT Capital Partners holds $41,190,000 worth of Golar LNG Limited (NASDAQ:GLNG) shares, representing 5.16% of its portfolio. With this, the company secures a...</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>RIT Capital Partners holds $41,190,000 worth of Golar LNG Limited (NASDAQ:GLNG) shares, representing 5.16% of its portfolio. With this, the company secures a spot on our list of billionaire Jacob Rot… [+1793 chars]</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>0.3818</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/chevron-wants-weigh-launch-venture-053256304.html</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2025-10-15T05:32:56Z</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Chevron Wants to Weigh In on the Launch of Venture Global’s New LNG Plant</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Chevron has asked regulators to let it weigh in on Venture Global’s request to delay its Plaquemines LNG project to 2027, fearing a repeat of past delivery...</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Chevron has requested to submit an opinion about a possible delay in the start-up of Venture Global’s second LNG plant, as the supermajor worries any delay would interfere with its delivery plans und… [+2578 chars]</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>-0.7506</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/germany-faces-40-billion-risk-220000002.html</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2025-10-09T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Germany Faces €40 Billion Risk If Winter Turns Cold</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>While ICIS argues that LNG imports and new regasification capacity can offset winter demand, rising prices and regulatory hurdles may threaten Germany’s...</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Germany could suffer economic losses of around 40 billion euros if this winter turns out colder than average, gas utility Uniper has warned in a report that said such a development could plunge Germa… [+4089 chars]</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>-0.8555</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/lng-boom-pricing-american-consumers-220000733.html</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2025-10-15T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>The LNG Boom That’s Pricing Out American Consumers</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Higher prices for U.S. natural gas seem to be inevitable as the main shale gas basins experience the same trends as oil basins.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>U.S. natural gas prices this week hit a two-week low on forecasts of a milder weather ahead. At $3.03 per mmBtu, natural gas was the lowest since late September—but it was significantly higher than i… [+5244 chars]</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>0.0772</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/european-unions-us-gas-set-112229166.html</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>By Nora Buli and Alban Kacher</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-10-06T11:22:29Z</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>European Union's US gas use set to soar, increasing price volatility</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>(Reuters) -Europe will need to import up to 160 additional liquefied natural gas cargoes this winter due to lower storage and a decline in pipeline flows...</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>By Nora Buli and Alban Kacher
+(Reuters) -Europe will need to import up to 160 additional liquefied natural gas cargoes this winter due to lower storage and a decline in pipeline flows from Russia an… [+2488 chars]</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>0.0772</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/cramer-backs-sempra-lng-expansion-142434158.html</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Venkatesh</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-10-08T14:24:34Z</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Cramer Backs Sempra as LNG Expansion and $10 Billion Deal Boost Outlook</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Sempra (NYSE:SRE) is one of the Jim Cramer’s Recession-Proof Stock Picks. One of Jim Cramer’s favorites from earlier this year, the company has announced a...</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Sempra (NYSE:SRE) is one of the Jim Cramers Recession-Proof Stock Picks.
+One of Jim Cramers favorites from earlier this year, the company has announced a final investment decision for Port Arthur LN… [+1948 chars]</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>0.6486</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/shell-greenlights-hi-offshore-gas-003219826.html</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-10-15T00:32:19Z</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Shell Greenlights HI Offshore Gas Project to Boost Nigeria LNG Supply</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Shell and local partner Sunlink Energies have reached a final investment decision (FID) on the HI gas project offshore Nigeria, which will deliver 350...</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Shell plc’s Nigerian subsidiary, Shell Nigeria Exploration and Production Company Limited (SNEPCo), has approved investment in the HI offshore gas development, marking another major step in expanding… [+3181 chars]</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>0.6705</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ypf-sociedad-nima-ypf-soared-044212607.html</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-10-13T04:42:12Z</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>YPF Sociedad Anónima (YPF) Soared This Week. Here is Why.</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>The share price of YPF Sociedad Anónima (NYSE:YPF) surged by 9.4% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained the ...</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>The share price of YPF Sociedad Anónima (NYSE:YPF) surged by 9.4% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+YPF Sociedad Anónima (YPF… [+1322 chars]</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>0.7096</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-stock-falls-losing-212414255.html</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Louis Juricic</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-10-09T21:24:14Z</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Venture Global stock falls after losing BP arbitration fight</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Investing.com -- Venture Global Inc. (NYSE: VG) stock fell 15% late on Thursday after the liquefied natural gas (LNG) exporter lost an arbitration dispute...</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Investing.com -- Venture Global Inc. (NYSE: VG) stock fell 15% late on Thursday after the liquefied natural gas (LNG) exporter lost an arbitration dispute with BP Plc (NYSE: BP) over cargo sales from… [+1373 chars]</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>-0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-market-braces-contango-shale-150000859.html</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-10-14T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Oil Market Braces for Contango and Shale Slowdown</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>The prospect of a contango is casting a shadow over oil markets, with the entire 2026 WTI futures curve now trading below $60 per barrel</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>The prospect of a contango is casting a shadow over oil markets, with the entire 2026 WTI futures curve now trading below $60 per barrelbeneath breakeven levels for most new shale wells. TotalEnergie… [+6281 chars]</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>0.5367</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eni-petronas-target-2026-launch-155704444.html</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2025-10-13T15:57:04Z</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Eni and Petronas Target 2026 Launch for Southeast Asia Gas Venture</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Eni is pushing ahead with its Southeast Asian expansion, targeting 2025 to launch a major gas joint venture with Malaysia’s Petronas</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Eni is pushing ahead with its Southeast Asian expansion, targeting 2025 to launch a major gas joint venture with Malaysia’s Petronas, part of a sweeping collaboration that could transform regional en… [+2419 chars]</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/golar-lng-limited-glng-bull-165615055.html</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Ricardo Pillai</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2025-10-08T16:56:15Z</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Golar LNG Limited (GLNG): A Bull Case Theory</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on Golar LNG Limited on X.com by gabcasla. In this article, we will summarize the bulls’ thesis on GLNG. Golar LNG Limited’s ...</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on Golar LNG Limited on X.com by gabcasla. In this article, we will summarize the bulls thesis on GLNG. Golar LNG Limited's share was trading at $40.57 as of September… [+2521 chars]</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>-0.1531</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/woodward-inc-wwd-spend-200-140211577.html</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Faheem Tahir</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2025-10-08T14:02:11Z</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Woodward, Inc. (WWD) to Spend $200 Million to Build 300,000-Square-Foot Factory; UBS Maintains Its Buy Rating with $299 PT</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>With significant hedge fund interest and trending on Reddit, Woodward, Inc. (NASDAQ:WWD) secures a spot on our list of the 10 Best Non-Tech Stocks to Buy...</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>With significant hedge fund interest and trending on Reddit, Woodward, Inc. (NASDAQ:WWD) secures a spot on our list of the 10 Best Non-Tech Stocks to Buy According to Reddit.
+Woodward, Inc. (WWD) to… [+1761 chars]</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>0.8834</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/excelerate-energy-ee-gains-following-044218423.html</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-10-13T04:42:18Z</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Excelerate Energy (EE) Gains Following New Award in Iraq</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>The share price of Excelerate Energy, Inc. (NYSE:EE) surged by 4.13% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained...</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>The share price of Excelerate Energy, Inc. (NYSE:EE) surged by 4.13% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Excelerate Energy (EE)… [+1827 chars]</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>0.9442</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/gold-overtake-lng-metallurgical-coal-054655806.html</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Paul-Alain Hunt</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-10-07T05:46:55Z</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Gold to Overtake LNG And Metallurgical Coal as Australia’s Second Most Valuable Export</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Revenues from bullion will jump to A$60 billion ($39.6 billion) in 2025-26 — the 12 month period to next June — up from A$47 billion in the prior year, and...</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>(Bloomberg) -- Gold will become Australias second-most-valuable commodity export, overtaking liquefied natural gas, after the precious metals extraordinary surge to record prices, the government said… [+2329 chars]</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>0.8622</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/uk-assures-ample-natural-gas-055100729.html</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-10-09T05:51:00Z</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>UK Assures Ample Natural Gas Supply for the Winter Months</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>The UK’s energy authorities say gas supplies will be sufficient this winter despite lower domestic production, with imports and renewables expected to fill...</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>There will be enough natural gas for the UK during the winter season, the country’s National Energy System Operator said in a report ahead of peak energy demand season. National Gas, the UK’s top sup… [+2351 chars]</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>0.8689</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/shells-q3-profit-soars-strong-120000486.html</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-10-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Shell's Q3 Profit Soars on Strong Trading and Production</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Shell anticipates a significant boost in its third-quarter earnings due to strong gas trading, increased upstream production, higher liquefaction volumes...</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Strong gas trading, higher upstream production and liquefaction volumes, and increased refining margins are expected to boost Shell’s third-quarter earnings, the supermajor said in a trading update o… [+2359 chars]</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>0.9231</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eni-ypf-advance-toward-final-042920247.html</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-10-13T04:29:20Z</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Eni and YPF Advance Toward Final Decision on Argentina LNG Megaproject</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Eni and YPF signed a key agreement to advance the 12 MTPA Argentina LNG project toward final investment approval.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Eni and YPF have signed a Final Technical Project Description to advance the 12 million-ton-per-year Argentina LNG project toward a Final Investment Decision, marking a major step in Argentina’s bid … [+2331 chars]</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/santos-cut-gas-production-guidance-094500155.html</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-10-16T09:45:00Z</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Santos Cut Gas Production Guidance on LNG Glitch and Floods</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Santos has cut its 2025 production forecast after software issues at the Barossa LNG project and flooding in the Cooper Basin disrupted operations.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Australia’s oil and gas giant Santos on Thursday lowered its production guidance for 2025 as a result of a software issue impacting the ramp-up of the new Barossa LNG project and floods in the Cooper… [+2335 chars]</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>-0.3818</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-empire-petroleum-ep-fell-012559182.html</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:25:59Z</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Here is Why Empire Petroleum (EP) Fell This Week</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>The share price of Empire Petroleum Corporation (NYSE:EP) fell by 9.52% between September 26 and October 3, 2025, putting it among the Energy Stocks that...</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>The share price of Empire Petroleum Corporation (NYSE:EP) fell by 9.52% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Here is Why Empire … [+1280 chars]</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-sabine-royalty-trust-sbr-012700666.html</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:27:00Z</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Here is Why Sabine Royalty Trust (SBR) Fell This Week</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>The share price of Sabine Royalty Trust (NYSE:SBR) fell by 8.27% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the...</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>The share price of Sabine Royalty Trust (NYSE:SBR) fell by 8.27% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Here is Why Sabine Royalty… [+1222 chars]</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>0.8225</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/gold-pass-lng-australia-no-150000904.html</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Andrew Topf</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2025-10-08T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Gold To Pass LNG As Australia’s No. 2 Resource Export</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>On Tuesday, Australia said it expects gold to become the country’s second most valuable resource after iron ore this financial year, eclipsing liquefied...</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Australia’s role as a resource powerhouse is changing due to global economic forces beyond its control: the fall in oil prices and the record-smashing increase in the price of gold.
+The country and … [+4148 chars]</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>0.0258</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/shell-boosts-lng-production-forecast-100610013.html</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Lekha Gupta</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2025-10-07T10:06:10Z</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Shell Boosts LNG Production Forecast As Refining Margins Surge</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Shell plc (NYSE:SHEL) shares were trading higher premarket on Tuesday after the company revised its third-quarter outlook. The oil giant trimmed the guidance...</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Shell plc (NYSE:SHEL) shares were trading higher premarket on Tuesday after the company revised its third-quarter outlook.
+The oil giant trimmed the guidance for production at Integrated Gas to arou… [+2233 chars]</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>0.5423</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/anfield-energy-aec-gained-almost-044214329.html</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2025-10-13T04:42:14Z</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Anfield Energy (AEC) Gained Almost 7% This Week. Here is Why.</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>The share price of Anfield Energy Inc. (NASDAQ:AEC) surged by 6.96% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained...</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>The share price of Anfield Energy Inc. (NASDAQ:AEC) surged by 6.96% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Anfield Energy (AEC) Ga… [+1790 chars]</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>0.9153</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/matador-resources-mtdr-falls-amid-012719133.html</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:27:19Z</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Matador Resources (MTDR) Falls Amid Declining Oil Prices</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>The share price of Matador Resources Company (NYSE:MTDR) fell by 8.14% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost...</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>The share price of Matador Resources Company (NYSE:MTDR) fell by 8.14% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Matador Resources (M… [+1440 chars]</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/houston-american-energy-husa-fell-012625322.html</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:26:25Z</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Houston American Energy (HUSA) Fell By 9% This Week. Here is Why.</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>The share price of Houston American Energy Corp. (NYSEAMERICAN:HUSA) fell by 9.05% between September 26 and October 3, 2025, putting it among the Energy...</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>The share price of Houston American Energy Corp. (NYSEAMERICAN:HUSA) fell by 9.05% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Houston … [+1524 chars]</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>0.6369</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/targa-resources-trgp-among-energy-012825552.html</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:28:25Z</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Targa Resources (TRGP): Among the Energy Stocks that Fell This Week</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>The share price of Targa Resources Corp. (NYSE:TRGP) fell by 6.83% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the...</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>The share price of Targa Resources Corp. (NYSE:TRGP) fell by 6.83% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Targa Resources (TRGP): … [+1478 chars]</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/northern-oil-gas-nog-among-012612873.html</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:26:12Z</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Northern Oil and Gas (NOG): Among the Energy Stocks that Fell This Week</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>The share price of Northern Oil and Gas, Inc. (NYSE:NOG) fell by 9.47% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost...</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>The share price of Northern Oil and Gas, Inc. (NYSE:NOG) fell by 9.47% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Northern Oil and Gas… [+1512 chars]</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/mizuho-downgrades-venture-global-vg-132717951.html</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2025-10-17T13:27:17Z</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Mizuho Downgrades Venture Global (VG) to Neutral After Losing BP Contract Breach Arbitration Case</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Venture Global Inc. (NYSE:VG) is one of the best young stocks with huge upside potential. On October 10, Mizuho analyst Gabriel Moreen downgraded Venture...</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Venture Global Inc. (NYSE:VG) is one of the best young stocks with huge upside potential. On October 10, Mizuho analyst Gabriel Moreen downgraded Venture Global to Neutral from Outperform with a pric… [+1632 chars]</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>0.5994</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/energy-fuels-uuuu-hits-fresh-044204240.html</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2025-10-13T04:42:04Z</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Energy Fuels (UUUU) Hits a Fresh High Amid the Escalating Trade War</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>The share price of Energy Fuels Inc. (NYSEAMERICAN:UUUU) surged by 23.12% between October 3 and October 10, 2025, putting it among the Energy Stocks that...</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>The share price of Energy Fuels Inc. (NYSEAMERICAN:UUUU) surged by 23.12% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Energy Fuels (UUU… [+1514 chars]</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>0.8225</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/baker-hughes-company-bkr-liquefaction-141309352.html</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Faheem Tahir</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2025-10-08T14:13:09Z</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Baker Hughes Company (BKR) to Provide Liquefaction Equipment for Sempra Infrastructure’s Port Arthur LNG Phase 2 Project in Texas</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>With significant hedge fund interest and return on equity, Baker Hughes Company (NASDAQ:BKR) secures a spot on our list of the 13 Safest Stocks to Invest in ...</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>With significant hedge fund interest and return on equity, Baker Hughes Company (NASDAQ:BKR) secures a spot on our list of the 13 Safest Stocks to Invest in Now.
+Baker Hughes Company (BKR) to Provid… [+1691 chars]</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>0.8316</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-vg-crashes-following-114005453.html</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2025-10-13T11:40:05Z</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Venture Global (VG) Crashes Following Arbitration Loss</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>The share price of Venture Global, Inc. (NYSE:VG) fell by 32.26% between October 3 and October 10, 2025, putting it among the Energy Stocks that Lost the...</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>The share price of Venture Global, Inc. (NYSE:VG) fell by 32.26% between October 3 and October 10, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Venture Global (VG) Crashes … [+1409 chars]</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>-0.0772</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/fortress-energy-nfe-negotiating-more-105209644.html</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Faheem Tahir</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2025-10-15T10:52:09Z</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>New Fortress Energy (NFE) Negotiating for More LNG Cargoes for Its Import Facilities Around the Americas</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>With significant upside potential, New Fortress Energy Inc. (NASDAQ:NFE) secures a spot on our list of the 7 best oil and gas penny stocks to buy according...</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>With significant upside potential, New Fortress Energy Inc. (NASDAQ:NFE) secures a spot on our list of the 7 best oil and gas penny stocks to buy according to analysts.
+New Fortress Energy Inc. (NFE… [+1812 chars]</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>0.9118000000000001</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/adnoc-listed-firms-target-43-063014242.html</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2025-10-09T06:30:14Z</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ADNOC Listed Firms Target $43 Billion in Dividends by 2030</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>ADNOC plans to distribute $43 billion in dividends through 2030, nearly doubling payouts since its first listing.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Abu Dhabi National Oil Company (ADNOC) unveiled an ambitious plan to distribute AED158 billion ($43 billion) in dividends across its six publicly listed subsidiaries by 2030—nearly twice the total am… [+4439 chars]</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jim-cramer-excelerate-energy-just-145818403.html</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Syeda Seirut Javed</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2025-10-09T14:58:18Z</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Jim Cramer on Excelerate Energy: “I Just Can’t Be Excited About It”</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Excelerate Energy, Inc. (NYSE:EE) is one of the stocks Jim Cramer put under the spotlight. When a caller expressed worry about the stock, Cramer remarked...</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Excelerate Energy, Inc. (NYSE:EE) is one of the stocks Jim Cramer put under the spotlight. When a caller expressed worry about the stock, Cramer remarked:
+Yeah, you know, I looked at that. I dont th… [+1863 chars]</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>0.5994</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ovintiv-ovv-fell-week-why-012937802.html</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:29:37Z</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Ovintiv (OVV) Fell This Week. Here is Why.</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>The share price of Ovintiv Inc. (NYSE:OVV) fell by 7.07% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This...</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>The share price of Ovintiv Inc. (NYSE:OVV) fell by 7.07% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Ovintiv (OVV) Fell This Week. Here… [+1302 chars]</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/fortress-energy-nfe-falls-over-113957055.html</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2025-10-13T11:39:57Z</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>New Fortress Energy (NFE) Falls Over Troubles in Puerto Rico Deal</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>The share price of New Fortress Energy Inc. (NASDAQ:NFE) fell by 13.02% between October 3 and October 10, 2025, putting it among the Energy Stocks that Lost ...</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>The share price of New Fortress Energy Inc. (NASDAQ:NFE) fell by 13.02% between October 3 and October 10, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+New Fortress Energy (… [+1571 chars]</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>0.5106000000000001</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/chinese-sanctions-hanwhas-us-shipbuilding-232412542.html</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2025-10-16T23:24:12Z</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Chinese sanctions on Hanwha's US shipbuilding units aim to 'coerce' South Korea, State Dept says</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>SEOUL (Reuters) -Chinese sanctions imposed this week on U.S. affiliates of shipbuilder Hanwha Ocean aim to undermine South Korea-U.S. cooperation and "to...</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>SEOUL (Reuters) -Chinese sanctions imposed this week on U.S. affiliates of shipbuilder Hanwha Ocean aim to undermine South Korea-U.S. cooperation and "to coerce" Washington's Asian ally, a U.S. State… [+1512 chars]</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>-0.3612</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jefferies-sees-positives-kimberly-clark-061212960.html</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Vardah Gill</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2025-10-15T06:12:12Z</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Jefferies Sees Positives in Kimberly-Clark’s (KMB) Energy Exposure but Says Upside is Limited</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Kimberly-Clark Corporation (NASDAQ:KMB) is included among the 11 Low PE High Dividend Stocks to Buy According to Analysts. On October 9, Jeffe​r⁠i‌es began...</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Kimberly-Clark Corporation (NASDAQ:KMB) is included among the 11 Low PE High Dividend Stocks to Buy According to Analysts.
+Jefferies Sees Positives in Kimberly-Clarks (KMB) Energy Exposure but Says … [+1676 chars]</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>0.7184</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/crescent-energy-crgy-among-energy-012912674.html</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:29:12Z</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Crescent Energy (CRGY): Among the Energy Stocks that Lost This Week</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>The share price of Crescent Energy Company (NYSE:CRGY) fell by 7.47% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost...</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>The share price of Crescent Energy Company (NYSE:CRGY) fell by 7.47% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Crescent Energy (CRGY)… [+1513 chars]</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>0.7269</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-isoenergy-ltd-isou-gained-044217276.html</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2025-10-13T04:42:17Z</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Here is Why IsoEnergy Ltd. (ISOU) Gained This Week</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>The share price of IsoEnergy Ltd. (NYSEAMERICAN:ISOU) surged by 5.7% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained...</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>The share price of IsoEnergy Ltd. (NYSEAMERICAN:ISOU) surged by 5.7% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Here is Why IsoEnergy … [+1631 chars]</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>0.8176</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/centrus-energy-leu-continues-gain-044215876.html</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2025-10-13T04:42:15Z</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Centrus Energy (LEU) Continues to Gain Amid a Renewed Focus on Uranium</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>The share price of Centrus Energy Corp. (NYSEAMERICAN:LEU) surged by 5.89% between October 3 and October 10, 2025, putting it among the Energy Stocks that...</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>The share price of Centrus Energy Corp. (NYSEAMERICAN:LEU) surged by 5.89% between October 3 and October 10, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Centrus Energy (… [+1602 chars]</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>0.9274</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-vital-energy-vtle-fell-012948405.html</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2025-10-06T01:29:48Z</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Here is Why Vital Energy (VTLE) Fell This Week</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>The share price of Vital Energy, Inc. (NYSE:VTLE) fell by 6.92% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the...</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>The share price of Vital Energy, Inc. (NYSE:VTLE) fell by 6.92% between September 26 and October 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Here is Why Vital Energy (V… [+1425 chars]</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>0.8979</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/totalenergies-anticipates-q3-earnings-boost-110000207.html</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2025-10-15T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>TotalEnergies Anticipates Q3 Earnings Boost on Production Surge</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>TotalEnergies anticipates higher third-quarter earnings and cash flow due to increased oil and gas production and a surge in refining margins, despite a...</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Despite the $10 per barrel decline in oil prices, TotalEnergies expects its earnings and cash flow to have increased in the third quarter from a year earlier, on the back of higher oil and gas produc… [+2610 chars]</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>0.5859</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/us-eases-penalties-tied-foreign-004344962.html</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>By Lisa Baertlein and David Lawder</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2025-10-11T00:43:44Z</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>US eases some penalties tied to foreign-built ships, toughens others</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>(Reuters) -The United States Trade Representative's office said on Friday it would modify certain maritime-related fees for foreign-built vehicle carriers...</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>By Lisa Baertlein and David Lawder
+(Reuters) -The United States Trade Representative's office said on Friday it would modify certain maritime-related fees for foreign-built vehicle carriers and liqu… [+2165 chars]</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>0.7184</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/much-earn-100-month-air-020105144.html</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>David Kirakosyan</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2025-10-11T02:01:05Z</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>How Much Would It Take To Earn $100 A Month From Air Products And Chemicals Stock</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Air Products and Chemicals Inc. (NYSE:APD) is a global leader in providing industrial gases, related equipment, and applications expertise to industries like...</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Benzinga and Yahoo Finance LLC may earn commission or revenue on some items through the links below.
+Air Products and Chemicals Inc. (NYSE:APD) is a global leader in providing industrial gases, rela… [+2115 chars]</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/alberta-seeks-federal-backing-oil-153000733.html</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2025-10-07T15:30:00Z</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Alberta Seeks Federal Backing for New Oil Pipeline</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Alberta Premier Danielle Smith is negotiating with the federal government and Prime Minister Mark Carney on the newly proposed oil pipeline from the oil...</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Alberta Premier Danielle Smith is negotiating with the federal government and Prime Minister Mark Carney on the newly proposed oil pipeline from the oil-producing province to the West Coast.
+Smith a… [+2558 chars]</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>0.0258</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/dwindling-gas-reserves-threaten-colombias-200000558.html</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Matthew Smith</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2025-10-09T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Dwindling Gas Reserves Threaten Colombia's Economy and Power Grid</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Colombia is facing a severe energy crisis due to declining natural gas production, dwindling reserves, and policies that are increasing its reliance on...</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Strife-torn South American country Colombia is not only suffering from a new wave of violence but is also facing an energy crisis. Dwindling oil and natural gas production is crimping domestic energy… [+6843 chars]</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>-0.5144</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/barclays-updates-price-target-duke-190928981.html</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2025-10-16T19:09:28Z</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Barclays Updates Price Target for Duke Energy (DUK)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Duke Energy Corporation (NYSE:DUK) is included among the 12 Best Nuclear Power Dividend Stocks to Buy Now. Duke Energy Corporation (NYSE:DUK) engages in the ...</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Duke Energy Corporation (NYSE:DUK) is included among the 12 Best Nuclear Power Dividend Stocks to Buy Now.
+Barclays Updates Price Target for Duke Energy (DUK) 
+Pixabay/Public Domain
+Duke Energy Co… [+1375 chars]</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>0.891</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/comstock-resources-crk-among-energy-114003346.html</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2025-10-13T11:40:03Z</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Comstock Resources (CRK) – Among the Energy Stocks that Fell This Week</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>The share price of Comstock Resources, Inc. (NYSE:CRK) fell by 12.95% between October 3 and October 10, 2025, putting it among the Energy Stocks that Lost...</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>The share price of Comstock Resources, Inc. (NYSE:CRK) fell by 12.95% between October 3 and October 10, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Comstock Resources (CRK… [+1334 chars]</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/energy-sector-outperforms-6-2-210000705.html</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Robert Rapier</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2025-10-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Energy Sector Outperforms with 6.2% Gain in Q3</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Markets carried momentum into Q3 2025, with the S&amp;P 500 advancing 7.8%, driven by moderating inflation and rising rate cut expectations, while the energy...</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Markets carried their momentum into the third quarter of 2025, even as political uncertainty and softer labor data kept investors cautious.
+The S&amp;amp;P 500 advanced 7.8% in Q3, a solid showing that … [+4895 chars]</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>0.6486</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/lng_sentiment_score_.xlsx
+++ b/data/lng_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G232"/>
+  <dimension ref="A1:G260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8595,6 +8595,996 @@
         <v>0.6486</v>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-talks-supply-ukraine-010759205.html</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2025-10-20T01:07:59Z</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Venture Global in Talks to Supply Ukraine With LNG as Winter Looms</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Venture Global is in talks with Ukraine’s DTEK for additional LNG cargoes amid mounting energy shortages caused by Russian attacks.</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Venture Global LNG (VG.N) has held discussions with Ukraine’s largest private energy company, DTEK, to supply additional cargoes of liquefied natural gas (LNG) from its Plaquemines facility in Louisi… [+3197 chars]</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/strong-natural-gas-demand-boosts-063000476.html</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2025-10-23T06:30:00Z</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Strong Natural Gas Demand Boosts Kinder Morgan's Q3 Performance</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Kinder Morgan posted a 16% rise in Q3 earnings per share as soaring global natural gas demand and growing LNG exports strengthened its long-term outlook.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Strong natural gas demand boosted the bottom line of Kinder Morgan in the third quarter, with the company reporting a 16% increase in earnings per share.
+“With historic growth in global natural gas … [+2428 chars]</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>0.9806</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-moves-closer-unofficial-072225220.html</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2025-10-21T07:22:25Z</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Venture Global Moves Closer to Unofficial Launch at Plaquemines</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Venture Global is moving ahead with early gas inflows at its Plaquemines LNG project, sparking renewed concern among long-term buyers after past disputes...</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Venture Global is ready to start feeding natural gas into its second LNG plant, Plaquemines, which is one of the last steps towards full-scale production.
+In a filing, the company said it was ready … [+2406 chars]</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>0.7579</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jera-buy-1-5-billion-073000060.html</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2025-10-23T07:30:00Z</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>JERA to Buy $1.5 Billion Worth of U.S. Shale Gas Assets</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Japan’s JERA will acquire $1.5 billion in natural gas assets in the U.S. Haynesville basin to expand its LNG supply chain and strengthen energy ties with the...</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Japan’s power generation major JERA will pay $1.5 billion for natural gas assets in the Haynesville basin, the company said today, in line with plans to boost its exposure to U.S. gas.
+The Japanese … [+2289 chars]</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>0.7964</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/nextdecade-approves-final-investment-decision-114143053.html</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2025-10-22T11:41:43Z</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NextDecade Approves Final Investment Decision for Train 5 at Rio Grande LNG Project</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>NextDecade Corporation (NASDAQ:NEXT) is one of the Reddit stocks that will go to the moon. On October 16, NextDecade Corporation announced that it had...</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>NextDecade Corporation (NASDAQ:NEXT) is one of the Reddit stocks that will go to the moon. On October 16, NextDecade Corporation announced that it had achieved a positive final investment decision/FI… [+1880 chars]</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>0.743</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/latest-us-strikes-2-more-122722073.html</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>The Associated Press</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2025-10-23T12:27:22Z</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>The Latest: US strikes 2 more alleged drug-carrying boats, this time in the Pacific Ocean</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>The U.S. military on Wednesday launched its ninth strike against an alleged drug-carrying vessel, killing three people in the eastern Pacific Ocean, Defense ...</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>The U.S. military on Wednesday launched its ninth strike against an alleged drug-carrying vessel, killing three people in the eastern Pacific Ocean, Defense Secretary Pete Hegseth said, expanding the… [+5677 chars]</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>-0.7506</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/nextdecade-corporation-next-bull-case-183223330.html</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Ricardo Pillai</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2025-10-22T18:32:23Z</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NextDecade Corporation (NEXT): A Bull Case Theory</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on NextDecade Corporation on wallstreetbets subreddit by nicefaygo. In this article, we will summarize the bulls’ thesis on...</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on NextDecade Corporation on wallstreetbets subreddit by nicefaygo. In this article, we will summarize the bulls thesis on NEXT. NextDecade Corporation's share was tra… [+2859 chars]</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>0.296</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/australia-woodside-lifts-oil-gas-100000284.html</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2025-10-22T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Australia’s Woodside Lifts Oil and Gas Production Guidance</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Woodside Energy raised its 2025 production outlook and lowered cost guidance on the back of strong asset performance, sending its shares higher.</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Woodside Energy, the biggest Australian oil and gas firm, on Wednesday raised its production guidance and lowered the expected production costs for 2025, citing the continued strong performance of it… [+2385 chars]</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>0.5994</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/russia-attempts-rare-risky-lng-093500166.html</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2025-10-20T09:35:00Z</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Russia Attempts Rare and Risky LNG Ship-to-Ship Transfer</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>A U.S.-sanctioned Russian LNG tanker appears to have carried out a rare ship-to-ship transfer off Malaysia, highlighting Moscow’s growing defiance of Western...</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>A sanctioned tanker carrying LNG from a U.S.-sanctioned export project in Russia appears to have undertaken a rare – and risky – ship-to-ship transfer of the LNG cargo off Malaysia, according to sate… [+2424 chars]</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>-0.3818</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/totalenergies-approves-restart-20-bn-163237484.html</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2025-10-25T16:32:37Z</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>TotalEnergies approves restart of $20-bn Mozambique gas project</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>France's TotalEnergies said Saturday the consortium it leads to build a $20-billion liquified natural gas project in Mozambique has decided to lift a...</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Work was frozen after jihadists launched a deadly attack on the site of the project near the Tanzanian border in March 2021 (Simon WOHLFAHRT)
+France's TotalEnergies said Saturday the consortium it l… [+1827 chars]</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>0.0258</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/scotiabank-slashes-pt-venture-global-114219496.html</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Noor Ul Ain Rehman</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2025-10-24T11:42:19Z</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Scotiabank Slashes PT on Venture Global (VG) to $13 From $16</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the best affordable stocks to buy under $20. On October 17, Scotiabank slashed the firm’s price target on Venture...</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the best affordable stocks to buy under $20. On October 17, Scotiabank slashed the firms price target on Venture Global, Inc. (NYSE:VG) to $13 from $16 while … [+1911 chars]</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>0.3612</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/lng-demand-fuels-strong-third-073000622.html</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2025-10-24T07:30:00Z</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>LNG Demand Fuels Strong Third Quarter for Baker Hughes</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Baker Hughes reported a strong third quarter driven by booming demand for LNG-related services, with record order backlogs offsetting weaker oilfield profits...</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Strong demand for LNG-related services drove Baker Hughes' third-quarter financial performance above expectations, with the company reporting a 23% annual increase in orders despite a dip in net prof… [+2326 chars]</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>0.7845</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/solaris-energy-infrastructure-sei-gains-061209805.html</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2025-10-21T06:12:09Z</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Solaris Energy Infrastructure (SEI) Gains Following Analyst Update</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>The share price of Solaris Energy Infrastructure, Inc. (NYSE:SEI) surged by 14.21% between October 10 and October 17, 2025, putting it among the Energy...</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>The share price of Solaris Energy Infrastructure, Inc. (NYSE:SEI) surged by 14.21% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Solaris… [+1285 chars]</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>0.8885</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/liberty-energy-lbrt-gains-amid-061207825.html</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2025-10-21T06:12:07Z</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Liberty Energy (LBRT) Gains Amid Positive Outlook for FY 2026</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>The share price of Liberty Energy Inc. (NYSE:LBRT) surged by 27.14% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained...</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>The share price of Liberty Energy Inc. (NYSE:LBRT) surged by 27.14% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Liberty Energy (LBRT) … [+1373 chars]</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>0.9786</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/select-water-solutions-wttr-gains-061214688.html</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2025-10-21T06:12:14Z</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Select Water Solutions (WTTR) Gains After Analyst Initiates Coverage</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>The share price of Select Water Solutions, Inc. (NYSE:WTTR) surged by 10.27% between October 10 and October 17, 2025, putting it among the Energy Stocks that...</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>The share price of Select Water Solutions, Inc. (NYSE:WTTR) surged by 10.27% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Select Water … [+1463 chars]</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>0.8658</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oklo-inc-oklo-hit-fresh-061211074.html</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2025-10-21T06:12:11Z</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Oklo Inc. (OKLO) Hit a Fresh High Following Newcleo Agreement</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>The share price of Oklo Inc. (NYSE:OKLO) surged by 11.03% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained the Most...</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>The share price of Oklo Inc. (NYSE:OKLO) surged by 11.03% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Oklo Inc. (OKLO) Hit a Fresh Hig… [+1770 chars]</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>0.9136</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jeffries-raises-price-target-oge-045635328.html</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2025-10-25T04:56:35Z</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Jeffries Raises its Price Target on OGE Energy (OGE)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>OGE Energy Corp. (NYSE:OGE) is included among the 12 Best Utility Stocks to Buy for Dividends. OGE Energy Corp. (NYSE:OGE), through its subsidiary, operates ...</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>OGE Energy Corp. (NYSE:OGE) is included among the 12 Best Utility Stocks to Buy for Dividends.
+Jeffries Raises its Price Target on OGE Energy (OGE)
+eliza-diamond-Iw2oRD2NP2w-unsplash
+OGE Energy Co… [+1522 chars]</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>0.891</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/brookfield-renewable-corporation-bepc-among-045553393.html</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2025-10-25T04:55:53Z</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Brookfield Renewable Corporation (BEPC) – Among the Best Utility Dividend Stocks to Buy Now</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Brookfield Renewable Corporation (NYSE:BEPC) is included among the 12 Best Utility Stocks to Buy for Dividends. Brookfield Renewable Corporation (NYSE:BEPC) ...</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Brookfield Renewable Corporation (NYSE:BEPC) is included among the 12 Best Utility Stocks to Buy for Dividends.
+Brookfield Renewable Corporation (BEPC) - Among the Best Utility Dividend Stocks to Bu… [+1607 chars]</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>0.9274</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/landbridge-company-lb-among-energy-061212651.html</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2025-10-21T06:12:12Z</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>LandBridge Company (LB) – Among the Energy Stocks that Gained This Week</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>The share price of LandBridge Company LLC (NYSE:LB) surged by 10.6% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained...</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>The share price of LandBridge Company LLC (NYSE:LB) surged by 10.6% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+LandBridge Company (LB… [+1659 chars]</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>0.8625</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/clearway-energy-cwen-receives-updated-045709865.html</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2025-10-25T04:57:09Z</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Clearway Energy (CWEN) Receives an Updated Price Target from CIBC</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Clearway Energy, Inc. (NYSE:CWEN) is included among the 12 Best Utility Stocks to Buy for Dividends. With a portfolio that comprises approximately 11.8 GW of...</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Clearway Energy, Inc. (NYSE:CWEN) is included among the 12 Best Utility Stocks to Buy for Dividends.
+Clearway Energy (CWEN) Receives an Updated Price Target from CIBC
+With a portfolio that comprise… [+1626 chars]</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>0.8591</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/teekay-tankers-tnk-gains-following-061215900.html</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2025-10-21T06:12:15Z</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Teekay Tankers (TNK) Gains Following Delay in Carbon Tax for Shipping</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>The share price of Teekay Tankers Ltd. (NYSE:TNK) surged by 9.63% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained the...</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>The share price of Teekay Tankers Ltd. (NYSE:TNK) surged by 9.63% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Teekay Tankers (TNK) Gai… [+1595 chars]</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>0.7184</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/brent-bounces-off-60-kazakh-154800477.html</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2025-10-21T15:48:00Z</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Brent Bounces Off $60 as Kazakh Cuts and Asian Demand Lift Prices</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Brent crude bounced back to $61 on Tuesday as Asian crude demand continues to show strength</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>We will then look at some of the key market movers early this week before providing you with the latest analysis of the top news events taking place in the global energy complex over the past few day… [+6554 chars]</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>0.0516</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/cheniere-energy-inc-lng-one-074644550.html</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Abdul Rahman</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2025-10-19T07:46:44Z</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Is Cheniere Energy, Inc. (LNG) One of the Most Profitable Energy Stocks to Buy Right Now?</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (NYSE:LNG) is one of the most profitable energy stocks to buy right now. On October 8, Goldman Sachs reiterated a ‘Buy’ rating on the...</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (NYSE:LNG) is one of the most profitable energy stocks to buy right now. On October 8, Goldman Sachs reiterated a Buy rating on the stock and raised the price target to $280 fro… [+1728 chars]</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>0.9196</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_aa037eac-d500-4a8e-ba0b-72892d914b7f</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2025-10-23T04:18:00Z</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Kinder Morgan Lifts Dividend as LNG Boom Powers 16% EPS Gain</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 237 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>0.8779</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-rises-nearly-5-fresh-133643465.html</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>By Enes Tunagur</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2025-10-23T13:36:43Z</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Oil rises nearly 5% on fresh US sanctions against Russia</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>By Enes Tunagur LONDON (Reuters) -Oil prices rose nearly 5% on Thursday after the U.S. imposed sanctions on major Russian suppliers Rosneft and Lukoil over...</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>By Enes Tunagur
+LONDON (Reuters) -Oil prices rose nearly 5% on Thursday after the U.S. imposed sanctions on major Russian suppliers Rosneft and Lukoil over Russia's war in Ukraine, extending gains f… [+2425 chars]</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>-0.128</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eni-raises-2025-cash-flow-100000570.html</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2025-10-24T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Eni Raises 2025 Cash Flow Guidance After Beating Q3 Estimates</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Eni raised its 2025 cash flow forecast and boosted buybacks by 20% after beating third-quarter profit expectations on higher oil and gas production.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Italy’s energy giant Eni (NYSE: E) raised its outlook on cash flow generation for 2025 and increased full-year planned buybacks by 20% after posting consensus-beating earnings for the third quarter.
+… [+2553 chars]</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>0.0516</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jera-expands-u-footprint-1-050000955.html</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2025-10-23T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>JERA Expands U.S. Footprint With $1.5 Billion Haynesville Shale Acquisition</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Japan’s largest power producer deepens U.S. energy ties with major upstream gas investment.</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>JERA Co. Inc., Japan’s largest power generation company, announced plans to acquire full ownership of the South Mansfield shale gas asset in Louisiana’s Haynesville Basin through its U.S. subsidiary … [+2624 chars]</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>0.4404</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/gasoline-prices-drop-toward-pandemic-000000953.html</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2025-10-22T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Gasoline Prices Drop Toward Pandemic-Era Lows</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>GasBuddy has predicted that prices will go even lower in the coming weeks, with good prospects of motorists enjoying sub-$3 prices for extended periods.</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>The national average price of gasoline dropped below $3 a gallon over the weekend, with many U.S. motorists now paying significantly less than they did a year ago. According to popular fuel savings p… [+5778 chars]</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>-0.0258</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/lng_sentiment_score_.xlsx
+++ b/data/lng_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G260"/>
+  <dimension ref="A1:G332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9585,6 +9585,2577 @@
         <v>-0.0258</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/us-japan-leaders-ink-rare-045356351.html</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>By Trevor Hunnicutt and Katya Golubkova</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2025-10-28T04:53:56Z</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>US, Japan leaders ink rare earths deal ahead of Trump-Xi meet this week</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>President Donald Trump and Japanese Prime Minister Sanae Takaichi signed a framework agreement on Tuesday for securing the supply of rare earths, as both...</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>By Trevor Hunnicutt and Katya Golubkova
+TOKYO (Reuters) -U.S. President Donald Trump and Japanese Prime Minister Sanae Takaichi signed a framework agreement on Tuesday for securing the supply of rar… [+3907 chars]</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>0.6705</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/videos/greece-ukraine-sign-us-gas-165153778.html</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Associated Press Videos</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2025-11-16T16:51:53Z</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Greece and Ukraine sign a US gas supply deal as Zelenskyy visits Athens</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>At a joint briefing with Greek Prime Minister Kyriakos Mitsotakis in Athens, Zelenskyy said the first gas deliveries from Greece will start in January. He...</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>At a joint briefing with Greek Prime Minister Kyriakos Mitsotakis in Athens, Zelenskyy said the first gas deliveries from Greece will start in January. He added the deal reached with Athens also incl… [+118 chars]</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>0.1027</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/big-techs-ai-power-needs-left-a-jerry-jones-backed-texas-gas-giant-sitting-on-the-holy-grail-of-supply-100101645.html</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Jake Conley</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2025-11-06T10:01:01Z</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Big Tech's AI power needs left a Jerry Jones-backed Texas gas giant sitting on the 'holy grail' of supply</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Natural gas producer Comstock Resources is capitalizing on stakes in one of the hottest gas regions in the country.</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>The AI boom has spiked energy demand, and as Big Tech firms and data center developers have scrounged for power, the fastest way to meet that demand has been with natural gas.
+In Texas, natural gas … [+7647 chars]</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>0.6249</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/u-invasion-venezuela-mean-global-180000673.html</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Cyril Widdershoven</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2025-11-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>What a U.S. Invasion of Venezuela Would Mean for Global Oil Prices</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>U.S. military preparations near Venezuela risk triggering a geopolitical and energy crisis that could disrupt global oil and gas markets, especially heavy...</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>The risks surrounding Venezuela, the world’s largest oil and gas reserves holder, are clearly skyrocketing. With Venezuela’s president, Maduro, calling upon Russia, China, and Iran to assist in a pos… [+8577 chars]</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>0.1531</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-q3-profit-surges-120229990.html</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2025-11-10T12:02:29Z</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Venture Global’s Q3 Profit Surges on Record LNG Exports</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Venture Global’s Q3 Profit Surges on Record LNG Exports</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Venture Global reported Q3 2025 revenue of $3.33 billion and net income of $429 million as record cargo exports and new SPAs lifted results, while the company narrowed full-year EBITDA guidance to $6… [+3594 chars]</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>0.4404</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/adnoc-secures-15-lng-supply-060000115.html</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2025-11-05T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>ADNOC Secures 15-Year LNG Supply Deal with Shell for Ruwais Project</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>ADNOC signs long-term LNG supply agreement with Shell, advancing the Ruwais project toward 2028 operations.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Abu Dhabi National Oil Company (ADNOC) has signed a 15-year sales and purchase agreement with Shell International Trading Middle East Limited for up to 1 million tons per annum (mtpa) of liquefied na… [+2565 chars]</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>0.5574</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/energy-transfer-seeks-lng-project-065150817.html</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2025-11-06T06:51:50Z</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Energy Transfer Seeks LNG Project Partners Before FID</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Energy Transfer will only proceed with the Lake Charles LNG project once it secures buyers for 80% of its equity, emphasizing capital discipline and risk...</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Energy Transfer will only make the final investment decision on the Lake Charles LNG project after it finds buyers for 80% of its equity, the company said in its third-quarter earnings call.
+The Lak… [+2238 chars]</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>0.4939</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-swings-massive-q3-163000490.html</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Michael Kern</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2025-11-10T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Venture Global Swings to Massive Q3 Profit as LNG Sales Explode</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Venture Global booked a net income of $429 million for the third quarter of 2025 as LNG sales and revenues soared, even while grappling with reduced EBITDA...</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>U.S. LNG exporter Venture Global (NYSE: VG) booked a net income for the third quarter, compared to a loss a year earlier, as revenues and LNG exports soared amid rising liquefaction capacity at its p… [+2691 chars]</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>0.1531</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/u-natural-gas-futures-skyrocket-220000193.html</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Andrew Topf</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2025-11-05T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>U.S. Natural Gas Futures Skyrocket on Record LNG Export Demand</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Fueled by a colder weather forecast and unprecedented LNG export demand from Europe and Asia, US natural gas prices have surged to a seven-month high...</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Cold, dry Arctic air moving across the central and eastern US early next week will cause temperatures to drop to 10-15 degrees below average, according to the Weather Prediction Center.
+The chilly f… [+4694 chars]</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>-0.0258</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/u-lng-boom-could-energy-160000018.html</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Kurt Cobb</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2025-10-27T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>The U.S. LNG Boom Could Make Energy More Expensive for Americans</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>America’s rapid expansion of liquefied natural gas (LNG) exports is tightening domestic supply and could drive up heating, electricity, and industrial costs ...</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>The noticeable upward tilt in graphs of the U.S. natural gas price since April 2024 is likely a hint of things to come for U.S. consumers of energy. That's because record amounts of U.S. natural gas … [+4320 chars]</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/australia-woodside-bets-big-lng-081017859.html</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2025-11-05T08:10:17Z</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Australia’s Woodside Bets Big on LNG Boom With 2032 Growth Plan</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Woodside Energy plans to boost oil and gas sales by 50% by 2032 through major LNG and crude expansion projects across Australia, the U.S., and Mexico.</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Australia’s Woodside Energy expects its sales of crude oil and natural gas to rise by some 50% by 2032, driven by growing demand for energy, especially in Asia.
+Growing at an annual rate of 6%, sale… [+2162 chars]</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>0.6969</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/shell-plc-shel-q3-2025-070030042.html</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>GuruFocus News</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2025-10-31T07:00:30Z</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Shell PLC (SHEL) Q3 2025 Earnings Call Highlights: Strong Financial Performance Amidst Market ...</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Shell PLC (SHEL) reports robust earnings and cash flow, while navigating challenges in the chemicals and LNG segments.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>This article first appeared on GuruFocus.
+Release Date: October 30, 2025
+For the complete transcript of the earnings call, please refer to the full earnings call transcript.
+&lt;ul&gt;&lt;li&gt;Shell PLC (NYS… [+3724 chars]</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>0.6808</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/natural-gas-prices-warm-5-144900966.html</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Nilanjan Choudhury</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2025-11-10T14:49:00Z</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Natural Gas Prices Warm Up 5% Amid Early Winter Forecasts</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>WMB, LNG, and EE emerge as key stocks as early winter forecasts, LNG exports, and steady demand fuel a third straight weekly rally.</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>The U.S. Energy Department’s latest storage report showed an injection slightly above analyst expectations but still below the five-year average, signaling steady market balance as the heating season… [+5365 chars]</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>0.4118</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/energy-majors-warn-eu-climate-200000984.html</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2025-11-12T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Energy Majors Warn EU Climate Push Could Gut Supply Security</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>The European Union is putting its energy security at risk by attempting to regulate every single molecule of energy products it will import in 2027, the year...</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>The European Union is putting its energy security at risk by attempting to regulate every single molecule of energy products it will import in 2027, the year in which the EU will ban Russian natural … [+6490 chars]</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>0.6705</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/brent-stalls-65-markets-shrug-160000783.html</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Michael Kern</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2025-11-04T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Brent Stalls at $65 as Markets Shrug Off OPEC+ Supply Signals</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>OPEC+’s efforts to calm fears of a 2026 oil glut failed to move crude prices, which remain flat near $65 per barrel amid subdued sentiment.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>OPEC+ has failed to spark an oil price rally with its commitment to halt production hikes in the first quarter of 2026, as fears of a supply glut continue to weigh on both Brent and WTI.
+Oil prices
+… [+7364 chars]</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>-0.3818</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/expand-energy-exe-one-best-133055153.html</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2025-10-30T13:30:55Z</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Is Expand Energy (EXE) One of the Best Up and Coming Stocks to Buy Right Now?</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Expand Energy Corporation (NASDAQ:EXE) is one of the best up and coming stocks to buy right now. On October 20, Kalei Akamine from Bank of America Securities...</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Expand Energy Corporation (NASDAQ:EXE) is one of the best up and coming stocks to buy right now. On October 20, Kalei Akamine from Bank of America Securities reiterated a Buy rating on Expand Energy,… [+1492 chars]</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>0.9623</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/siebert-williams-shank-maintains-buy-135652069.html</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2025-10-30T13:56:52Z</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Siebert Williams Shank Maintains Buy Rating, $132 PT on Expand Energy (EXE)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Expand Energy Corporation (NASDAQ:EXE) is one of the most undervalued large cap stocks to buy right now. On October 29, Siebert Williams Shank &amp; Co...</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Expand Energy Corporation (NASDAQ:EXE) is one of the most undervalued large cap stocks to buy right now. On October 29, Siebert Williams Shank &amp;amp; Co. maintained a Buy rating on Expand Energy, with… [+1650 chars]</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>0.8807</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/williams-posts-solid-ebitda-growth-015410062.html</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:54:10Z</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Williams Posts Solid EBITDA Growth Despite Higher Costs</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>U.S. pipeline operator delivers double-digit operating gains as Transco and Gulf volumes rise, reaffirming 2025 guidance.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Williams (NYSE: WMB) reported a 13% year-over-year increase in adjusted EBITDA to $1.92 billion for the third quarter of 2025, driven by new capacity on its Transco pipeline and higher Gulf of Mexico… [+3069 chars]</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>0.6705</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/tc-energy-upbeat-north-america-173000071.html</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Michael Kern</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2025-11-06T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>TC Energy Upbeat on North America’s Natural Gas Market</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Despite slightly missing third-quarter analyst estimates, TC Energy is highly optimistic about a massive surge in North American natural gas demand driven by...</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>While TC Energy slightly missed analyst estimates of its third-quarter earnings, the Canada-based pipeline operator expects North American natural gas demand to surge in the medium to long term, than… [+3025 chars]</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>0.6997</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jera-profit-climbs-despite-lower-030310651.html</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2025-10-31T03:03:10Z</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>JERA Profit Climbs Despite Lower Revenues Amid Fuel Price Headwinds</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Japan’s largest power generator saw a profit rise on improved overseas and renewable performance.</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>JERA Co., Inc., Japan’s largest power generation company and one of the world’s leading LNG importers, reported a rise in second-quarter profit for fiscal 2025 despite a decline in overall revenue, d… [+4010 chars]</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>0.7709</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-unmoved-trump-xi-193100458.html</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Michael Kern</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2025-10-31T19:31:00Z</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Oil Prices Unmoved by Trump-Xi Meeting</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>This report provides an overview of global oil and natural gas market trends, including price changes, production data, and geopolitical developments...</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>This report provides an overview of global oil and natural gas market trends, including price changes, production data, and geopolitical developments impacting energy.
+The Trump-Xi meeting in South … [+4931 chars]</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>0.5574</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/china-leads-world-underground-gas-163000487.html</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2025-10-27T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>China Leads World’s Underground Gas Storage Buildup</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>China has increased its underground gas storage capacity by the most of any country since 2022, the International Gas Union (IGU) said in a new report on...</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>China has increased its underground gas storage capacity by the most of any country since 2022, the International Gas Union (IGU) said in a new report on Monday.
+As of 2025, there are 699 undergroun… [+2368 chars]</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/exxon-crushes-q3-forecasts-record-193000428.html</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Julianne Geiger</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2025-10-31T19:30:00Z</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Exxon Crushes Q3 Forecasts on Record Guyana and Permian Output</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Exxon Mobil exceeded third-quarter earnings forecasts, reporting $8.1 billion in adjusted earnings due to record output from Guyana and the Permian Basin...</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Exxon Mobil (NYSE: XOM) topped Wall Street expectations for the third quarter, posting $8.1 billion in adjusted earnings, or $1.88 per share—up from $7.1 billion in Q2—on record output from Guyana an… [+2457 chars]</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>-0.4404</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eni-ypf-adnoc-xrg-advance-150000100.html</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2025-11-05T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Eni, YPF, and ADNOC’s XRG Advance Talks on Argentina LNG Megaproject</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Eni and YPF have signed a framework deal with ADNOC’s XRG for potential participation in Argentina’s 12 MTPA LNG phase.</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Eni and Argentina’s state-backed energy major YPF have signed a non-binding agreement with XRG, a subsidiary of the Abu Dhabi National Oil Company (ADNOC) Group, to explore potential collaboration on… [+2613 chars]</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>0.6486</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/abu-dhabi-xrg-talks-join-184000505.html</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2025-10-27T18:40:00Z</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Abu Dhabi’s XRG in Talks to Join YPF’s LNG Export Venture</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Abu Dhabi National Oil Company’s overseas arm, XRG, is in early talks to invest in Argentina’s first large-scale liquefied natural gas (LNG) project, led by ...</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Abu Dhabi National Oil Company’s overseas arm, XRG, is in early talks to invest in Argentina’s first large-scale liquefied natural gas (LNG) project, led by state-owned YPF SA. The move aligns with X… [+2428 chars]</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>0.5719</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/shell-tops-profit-estimates-higher-112634248.html</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2025-10-30T11:26:34Z</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Shell Tops Profit Estimates on Higher Output and Strong Trading</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Shell’s third-quarter earnings beat expectations as higher LNG production, trading profits, and refining margins offset weaker oil prices, supporting another...</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Shell (NYSE: SHEL) posted consensus-beating earnings for the third quarter as higher oil and LNG production, higher trading profits, and improved refining margins partly offset the decline in oil pri… [+2391 chars]</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>0.9382</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/analysts-eye-big-oils-spending-220000657.html</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2025-10-30T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Analysts Eye Big Oil's Spending and Acquisition Plans</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Big Oil companies are reporting third-quarter results, with analysts keenly focused on their 2026 strategies, particularly their investments in LNG and plans...</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Big Oil is reporting third-quarter results this week and next. No surprises are expected—Big Oil has been having an eventful year featuring tariffs, sanctions, and glut predictions—and these events w… [+4328 chars]</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>-0.0772</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/totalenergies-cash-flow-snaps-back-161354565.html</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Moz Farooque ACCA</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2025-10-30T16:13:54Z</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>TotalEnergies' Cash Flow Snaps Back as Oil Prices Cool</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Solid Q3 shows financial discipline paying off despite a softer top line.</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>This article first appeared on GuruFocus.
+TotalEnergies (NYSE:TTE) delivered a mixed but encouraging third quarter profit came in a touch below expectations, but cash flow came roaring back. The com… [+858 chars]</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>0.8779</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/research/reports/ARGUS_45313_MarketSummary_1763120032000/</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2025-11-14T11:33:52Z</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Market Digest: DIS, DTE, FCX, MGM, NYT, VRSK, LEA, LNG</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>At Yahoo Finance, you get free stock quotes, up-to-date news, portfolio management resources, international market data, social interaction and mortgage rates that help you manage your financial life.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Sector(s) 
+Communication Services, Utilities, Energy, Basic Materials, Industrials, Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/totalenergies-tte-falls-short-estimates-010024170.html</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:00:24Z</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>TotalEnergies (TTE) Falls Short of Estimates in Q3</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>TotalEnergies SE (NYSE:TTE) is included among the 11 Best High Yield Energy Stocks to Buy Now. TotalEnergies SE (NYSE:TTE) is a global integrated energy...</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>TotalEnergies SE (NYSE:TTE) is included among the 11 Best High Yield Energy Stocks to Buy Now.
+TotalEnergies (TTE) Falls Short of Estimates in Q3
+TotalEnergies SE (NYSE:TTE) is a global integrated … [+1629 chars]</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>0.743</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/investors-reacting-energy-transfer-et-121308155.html</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Simply Wall St</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2025-10-29T12:13:08Z</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>How Investors Are Reacting To Energy Transfer (ET) Raising Its Quarterly Distribution by Over 3 Percent</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Energy Transfer LP recently announced an increase in its quarterly cash distribution to US$0.3325 per common unit for the third quarter ended September 30...</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;&lt;li&gt;Energy Transfer LP recently announced an increase in its quarterly cash distribution to US$0.3325 per common unit for the third quarter ended September 30, 2025, with payment scheduled for No… [+3749 chars]</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>0.5266999999999999</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/shell-profit-jumps-stronger-trading-075627768.html</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Vahid Karaahmetovic</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2025-10-30T07:56:27Z</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Shell profit jumps on stronger trading and higher volumes; new $3.5 bln buyback</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Investing.com -- Shell reported a solid rebound in profitability in the third quarter of 2025, driven by stronger trading, higher sales volumes, and...</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Investing.com -- Shell reported a solid rebound in profitability in the third quarter of 2025, driven by stronger trading, higher sales volumes, and favorable tax movements.
+Income attributable to s… [+2370 chars]</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>0.9169</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/conocophillips-hits-gas-discovery-australia-064500669.html</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2025-11-17T06:45:00Z</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>ConocoPhillips Hits New Gas Discovery in Australia’s Otway Basin</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>ConocoPhillips has made a promising natural gas discovery in Australia’s Otway Basin, marking the region’s first find since 2021 and raising new questions...</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>ConocoPhillips has made a natural gas discovery in the Otway Basin off the Australian coast, the company said today, adding that the reserves tapped and their commercial viability have yet to be esti… [+2277 chars]</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>0.3612</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-vg-receives-final-013833420.html</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Ali Ahmed</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2025-10-31T01:38:33Z</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Venture Global (VG) Receives Final Approval to Export LNG from CP2 Plant</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the 10 Stocks Under $20 to Buy According to Analysts. On October 22, Venture Global, Inc. (NYSE:VG) announced that...</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the 10 Stocks Under $20 to Buy According to Analysts. On October 22, Venture Global, Inc. (NYSE:VG) announced that the US Department of Energy gave the final … [+1648 chars]</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>0.6369</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ypf-sociedad-ypf-soars-23-092536230.html</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Angelica Ballesteros</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2025-10-28T09:25:36Z</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>YPF Sociedad (YPF) Soars 23.78% as Abu Dhabi Firm Eyes Investment</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>We recently published 10 Big Names Crushing Wall Street. YPF Sociedad Anonima (NYSE:YPF) is one of the top-performing stocks on Monday. YPF Sociedad extended...</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>We recently published 10 Big Names Crushing Wall Street. YPF Sociedad Anonima (NYSE:YPF) is one of the top-performing stocks on Monday.
+YPF Sociedad extended its winning streak to a 4th consecutive … [+1706 chars]</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>0.2263</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/goldman-sachs-says-ai-boom-230000443.html</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2025-11-10T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Goldman Sachs Says AI Boom Will Supercharge Energy Demand</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Goldman Sachs dismisses fears of an AI stock market bubble but warns that the rapid growth of AI data centers will dramatically increase US energy...</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Lately, big tech cheerleaders, including Meta Platforms’ (NASDAQ:META) Mark Zuckerberg, Amazon’s (NASDAQ:AMZN) Jeff Bezos and OpenAI’s CEO Sam Altman, have warned we are in an AI bubble, with stock m… [+4719 chars]</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>0.1779</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/indias-ongc-eyes-strong-output-185910526.html</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2025-11-11T18:59:10Z</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>India's ONGC Eyes Strong Output Growth Next Year</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>India’s state-run Oil and Natural Gas Corporation (ONGC) expects to produce 21 million metric tonnes (MMT) of crude oil and 21.5 billion cubic meters (BCM...</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>India’s state-run Oil and Natural Gas Corporation (ONGC) expects to produce 21 million metric tonnes (MMT) of crude oil and 21.5 billion cubic meters (BCM) of natural gas in the next fiscal year (FY2… [+2428 chars]</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>0.7351</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/delek-us-holdings-dk-gains-054653659.html</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2025-10-28T05:46:53Z</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Delek US Holdings (DK) Gains Following Price Target Update</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>The share price of Delek US Holdings, Inc. (NYSE:DK) surged by 10.13% between October 17 and October 24, 2025, putting it among the Energy Stocks that Gained...</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>The share price of Delek US Holdings, Inc. (NYSE:DK) surged by 10.13% between October 17 and October 24, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Delek US Holdings (D… [+1287 chars]</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>0.8074</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-slide-as-meta-sinks-after-earnings-with-apple-amazon-ahead-133548029.html</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2025-10-30T13:35:48Z</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq slide after Trump-Xi truce with Big Tech earnings ahead</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Wall Street eyed a US-China truce agreed by Trump and Xi, cooling hopes for a December rate cut and the next batch of Big Tech earnings.</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Economic data: Initial jobless claims (week ended October 25); Continuing claims (week ended October 18); Personal consumption (third quarter); GDP annualized (third quarter)
+Earnings calendar: Appl… [+1205 chars]</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-vg-recoups-7-182707589.html</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Angelica Ballesteros</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2025-11-13T18:27:07Z</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Venture Global (VG) Recoups 7.9% Gain on Bagging 2 Multi-Year Supply Deals</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>We recently published Market Beaters: 10 Stocks Defying the Odds. Venture Global Inc. (NYSE:VG) is one of the best-performing stocks on Wednesday. Venture...</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>We recently published Market Beaters: 10 Stocks Defying the Odds. Venture Global Inc. (NYSE:VG) is one of the best-performing stocks on Wednesday.
+Venture Global bounced back by 7.86 percent on Wedn… [+1784 chars]</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>0.5266999999999999</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/conocophillips-lifts-dividend-8-raises-011143125.html</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2025-11-07T01:11:43Z</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ConocoPhillips Lifts Dividend 8% and Raises 2025 Output</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>ConocoPhillips reported Q3 results, increased its base dividend, and issued initial 2026 spending and cost guidance.</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>ConocoPhillips posted Q3 2025 adjusted EPS of $1.61, raised its ordinary dividend by 8% to $0.84 per share, lifted full-year production guidance to 2.375 MMBOED, trimmed 2025 operating cost guidance,… [+3607 chars]</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>0.296</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/exclusive-pakistan-cancels-eni-lng-100329715.html</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>By Ariba Shahid</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2025-11-04T10:03:29Z</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Exclusive-Pakistan cancels Eni LNG cargoes, seeks to renegotiate Qatar supplies</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>KARACHI (Reuters) -Pakistan has struck a deal to cancel 21 liquefied natural gas cargoes under its long-term contract with Italy's Eni as part of a plan to...</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>By Ariba Shahid
+KARACHI (Reuters) -Pakistan has struck a deal to cancel 21 liquefied natural gas cargoes under its long-term contract with Italy's Eni as part of a plan to curb excess imports that h… [+2440 chars]</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/comstock-resources-crk-posts-impressive-020413933.html</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2025-11-11T02:04:13Z</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Comstock Resources (CRK) Posts Impressive Performance in Q3</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>The share price of Comstock Resources, Inc. (NYSE:CRK) surged by 22.77% between October 31 and November 7, 2025, putting it among the Energy Stocks that...</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>The share price of Comstock Resources, Inc. (NYSE:CRK) surged by 22.77% between October 31 and November 7, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Comstock Resources… [+1995 chars]</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>0.8481</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/dt-midstream-inc-dtm-q3-203853502.html</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>GuruFocus News</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2025-10-30T20:38:53Z</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DT Midstream Inc (DTM) Q3 2025 Earnings Call Highlights: Strong Financial Performance and ...</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>DT Midstream Inc (DTM) reports robust growth in adjusted EBITDA and unveils significant pipeline expansions amid competitive challenges.</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Q: Can you expand on the potential for your network to support data center demand in Louisiana? A: David Slater, President and CEO, explained that there is significant demand materializing in Louisia… [+1824 chars]</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>0.7964</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/chevron-corporation-cvx-reports-strong-010451862.html</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:04:51Z</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (CVX) Reports Strong Results for Q3 Despite Low Prices</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 11 Best High Yield Energy Stocks to Buy Now. Chevron Corporation (NYSE:CVX) manufactures and sells a...</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is included among the 11 Best High Yield Energy Stocks to Buy Now.
+Chevron Corporation (CVX) Reports Strong Results for Q3 Despite Low Prices
+Chevron Corporation (NYS… [+1635 chars]</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>0.9385</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/weatherford-international-wfrd-gains-despite-054652367.html</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2025-10-28T05:46:52Z</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Weatherford International (WFRD) Gains Despite Missing Estimates in Q3</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>The share price of Weatherford International plc (NASDAQ:WFRD) surged by 13.02% between October 17 and October 24, 2025, putting it among the Energy Stocks...</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>The share price of Weatherford International plc (NASDAQ:WFRD) surged by 13.02% between October 17 and October 24, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Weatherfor… [+1622 chars]</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>0.8477</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jeffries-analyst-initiates-coverage-energy-005934689.html</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2025-11-04T00:59:34Z</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Jeffries Analyst Initiates Coverage on Energy Transfer (ET)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Energy Transfer LP (NYSE:ET) is included among the 11 Best High Yield Energy Stocks to Buy Now. Energy Transfer LP (NYSE:ET) is one of the largest and most...</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Energy Transfer LP (NYSE:ET) is included among the 11 Best High Yield Energy Stocks to Buy Now.
+Jeffries Analyst Initiates Coverage on Energy Transfer (ET)
+Energy Transfer LP (NYSE:ET) is one of th… [+1580 chars]</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>0.9136</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/northwestern-energy-group-nwe-reports-010401113.html</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:04:01Z</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NorthWestern Energy Group (NWE) Reports Strong Results for Q3</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>NorthWestern Energy Group, Inc. (NASDAQ:NWE) is included among the 11 Best High Yield Energy Stocks to Buy Now. NorthWestern Energy Group, Inc. (NASDAQ:NWE) ...</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>NorthWestern Energy Group, Inc. (NASDAQ:NWE) is included among the 11 Best High Yield Energy Stocks to Buy Now.
+NorthWestern Energy Group (NWE) Reports Strong Results for Q3
+NorthWestern Energy Gro… [+1579 chars]</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>0.9601</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/viper-energy-vnom-one-best-011255575.html</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:12:55Z</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Viper Energy (VNOM) – One of the Best High Yield Energy Stocks to Buy Now</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Viper Energy, Inc. (NASDAQ:VNOM) is included among the 11 Best High Yield Energy Stocks to Buy Now. Viper Energy, Inc. (NASDAQ:VNOM) is a publicly traded...</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Viper Energy, Inc. (NASDAQ:VNOM) is included among the11 Best High Yield Energy Stocks to Buy Now.
+Viper Energy (VNOM) - One of the Best High Yield Energy Stocks to Buy Now
+Viper Energy, Inc. (NASD… [+1632 chars]</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>0.9758</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/sunoco-sun-receives-upgrade-wells-011238108.html</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:12:38Z</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Sunoco (SUN) Receives an Upgrade from Wells Fargo</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Sunoco LP (NYSE:SUN) is included among the 11 Best High Yield Energy Stocks to Buy Now. Sunoco LP (NYSE:SUN) is a leading operator of critical energy...</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Sunoco LP (NYSE:SUN) is included among the11 Best High Yield Energy Stocks to Buy Now.
+Sunoco (SUN) Receives an Upgrade from Wells Fargo
+Sunoco LP (NYSE:SUN) is a leading operator of critical energ… [+1663 chars]</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>0.7906</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/top-research-reports-tesla-blackrock-212100082.html</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Mark Vickery</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2025-11-05T21:21:00Z</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Top Research Reports for Tesla, BlackRock &amp; Welltower</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Tesla sets delivery records but braces for weaker Q4 as tax credits expire and competition heats up.</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Wednesday, November 5, 2025
+The Zacks Research Daily presents the best research output of our analyst team. Today's Research Daily features new research reports on 16 major stocks, including Tesla, … [+8537 chars]</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>0.7184</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/tc-energy-q3-earnings-match-132600472.html</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Zacks Equity Research</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2025-11-10T13:26:00Z</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>TC Energy Q3 Earnings Match Estimates, Revenues Beat, Both Fall Y/Y</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>TRP anticipates its 2025 comparable EBITDA to be between C$10.8 billion and C$11 billion, with net Capex to be between C$5.5 billion and C$6 billion.</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>TC Energy Corporation TRP reported third-quarter 2025 adjusted earnings of 56 cents per share, which came in line with the Zacks Consensus Estimate.This performance was driven by robust results from … [+7623 chars]</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>0.7783</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-prices-surge-5-us-151820545.html</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2025-10-23T15:18:20Z</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Oil prices surge 5% as US hits Russian firms Rosneft, Lukoil with sanctions</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>NEW YORK (Reuters) -Oil prices surged around 5% to a two-week high on Thursday after the U. imposed sanctions on major Russian suppliers Rosneft and Lukoil...</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>By Scott DiSavino
+NEW YORK (Reuters) -Oil prices surged around 5% to a two-week high on Thursday after the U.S. imposed sanctions on major Russian suppliers Rosneft and Lukoil over Russia's war in U… [+3595 chars]</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>-0.6369</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/antero-resources-stock-gains-4-143500448.html</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Zacks Equity Research</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2025-11-06T14:35:00Z</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Antero Resources Stock Gains 4% Despite Q3 Earnings Miss</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>AR gains as rising gas demand offsets Q3 earnings miss, with stronger production and pricing momentum.</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Antero Resources Corporation AR rose 3.8% despite reporting lower-than-expected earnings on Oct. 29. This signifies rising natural gas demand backed by power-hungry data centers and increasing LNG ex… [+3785 chars]</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>0.6052</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trump-sanctions-light-fire-under-150316124.html</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2025-10-24T15:03:16Z</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Trump’s Sanctions Light a Fire Under Oil Prices</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Oil markets roared back to life after Trump’s sanctions on Russia’s top oil producers sent prices surging.</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Oil markets roared back to life after Trumps sanctions on Russias top oil producers sent prices surging.
+Friday, October 24, 2025
+Trumps sanctions on Russias top oil firms have cut short the past w… [+5138 chars]</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>-0.2263</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/factbox-whats-agenda-us-japan-014833113.html</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2025-10-28T01:48:33Z</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Factbox-What's on the agenda for US-Japan talks?</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>President Donald Trump and Japan's Prime Minister Sanae Takaichi are holding talks on security and trade in Tokyo on Tuesday, marking his first visit to...</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>(Reuters) -U.S. President Donald Trump and Japan's Prime Minister Sanae Takaichi are holding talks on security and trade in Tokyo on Tuesday, marking his first visit to Japan since 2019.
+The followi… [+4250 chars]</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bp-among-best-high-yield-005919250.html</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2025-11-04T00:59:19Z</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>BP – Among the Best High Yield Energy Stocks to Buy Now</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>BP p.l.c. (NYSE:BP) is included among the 11 Best High Yield Energy Stocks to Buy Now. BP p.l.c. (NYSE:BP) is a British multinational company recognized...</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>BP p.l.c. (NYSE:BP) is included among the 11 Best High Yield Energy Stocks to Buy Now.
+BP - Among the Best High Yield Energy Stocks to Buy Now
+BP p.l.c. (NYSE:BP) is a British multinational company… [+2200 chars]</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>0.9578</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/enbridge-inc-enb-bull-case-023153530.html</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Ricardo Pillai</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2025-10-22T02:31:53Z</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Enbridge Inc. (ENB): A Bull Case Theory</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on Enbridge Inc. on Beat the TSX (BTSX-20)’s Substack by Beat the TSX-27 Strategy. In this article, we will summarize the...</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on Enbridge Inc. on Beat the TSX (BTSX-20)s Substack by Beat the TSX-27 Strategy. In this article, we will summarize the bulls thesis on ENB. Enbridge Inc.'s share was… [+2655 chars]</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>0.296</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/dominion-energy-d-beats-expectations-010248462.html</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:02:48Z</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Dominion Energy (D) Beats Expectations in Q3 Report</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Dominion Energy, Inc. (NYSE:D) is included among the 11 Best High Yield Energy Stocks to Buy Now. Dominion Energy, Inc. (NYSE:D) provides regulated...</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Dominion Energy, Inc. (NYSE:D) is included among the 11 Best High Yield Energy Stocks to Buy Now.
+Dominion Energy (D) Beats Expectations in Q3 Report
+Pixabay/Public Domain
+Dominion Energy, Inc. (N… [+2139 chars]</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>0.9136</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/nordic-american-tankers-nat-surges-061218101.html</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2025-10-21T06:12:18Z</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Nordic American Tankers (NAT) Surges Amid Boost for Shipping Industry</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>The share price of Nordic American Tankers Limited (NYSE:NAT) surged by 8.07% between October 10 and October 17, 2025, putting it among the Energy Stocks...</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>The share price of Nordic American Tankers Limited (NYSE:NAT) surged by 8.07% between October 10 and October 17, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Nordic Ameri… [+1857 chars]</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/enbridge-enb-receives-bullish-stance-010041524.html</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:00:41Z</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Enbridge (ENB) Receives Bullish Stance from Analysts</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Enbridge Inc. (NYSE:ENB) is included among the 11 Best High Yield Energy Stocks to Buy Now. Enbridge Inc. (NYSE:ENB) is a midstream energy company that...</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Enbridge Inc. (NYSE:ENB) is included among the 11 Best High Yield Energy Stocks to Buy Now.
+Enbridge (ENB) Receives Bullish Stance from Analysts
+Enbridge Inc. (NYSE:ENB) is a midstream energy compa… [+2131 chars]</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>0.8126</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/factbox-whats-agenda-us-japan-022943749.html</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2025-10-28T02:29:43Z</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Factbox-What's on the agenda for US-Japan talks?</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>President Donald Trump and Japan's Prime Minister Sanae Takaichi are holding talks on security and trade in Tokyo on Tuesday, marking his first visit to...</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>(Reuters) -U.S. President Donald Trump and Japan's Prime Minister Sanae Takaichi are holding talks on security and trade in Tokyo on Tuesday, marking his first visit to Japan since 2019.
+The followi… [+4396 chars]</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/factbox-corporate-concerns-mount-ahead-182839257.html</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2025-10-27T18:28:39Z</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Factbox-Corporate concerns mount ahead of Trump and Xi talks in South Korea</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>() -Global companies have a long list of concerns around the U. They will closely monitor President Donald Trump and Chinese President Xi Jinping's expected ...</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>(Reuters) -Global companies have a long list of concerns around the U.S.-China trade war. They will closely monitor President Donald Trump and Chinese President Xi Jinping's expected meeting in South… [+5819 chars]</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>-0.5994</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/goldman-sachs-keeps-buy-rating-030749471.html</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Ali Ahmed</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2025-10-21T03:07:49Z</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Goldman Sachs Keeps Buy Rating on Venture Global (VG) After Arbitration Decision</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the 11 Dirt Cheap Stocks to Buy According to Analysts. On October 16, Goldman Sachs reduced its price target on...</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the 11 Dirt Cheap Stocks to Buy According to Analysts. On October 16, Goldman Sachs reduced its price target on Venture Global, Inc. (NYSE:VG) from $18 to $17… [+2020 chars]</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/morgan-stanley-reduces-pt-conocophillips-130827363.html</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Bob Karr</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2025-10-30T13:08:27Z</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Morgan Stanley Reduces PT on ConocoPhillips (COP) Stock</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is one of the Best Bargain Stocks to Buy in November. On October 14, Morgan Stanley analyst Devin McDermott reduced the price...</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is one of the Best Bargain Stocks to Buy in November.On October 14, Morgan Stanley analyst Devin McDermott reduced the price objective on the companys stock to $122 from $12… [+2429 chars]</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>0.7184</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-rises-sanctions-hit-russian-151500767.html</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2025-11-11T15:15:00Z</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Oil Rises as Sanctions Hit Russian Exports and Lukoil Declares Force Majeure</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Oil prices gained on Tuesday as fresh U.S. sanctions on Russian oil disrupted exports and prompted Lukoil to declare force majeure at one of its Iraqi fields...</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Oil prices gained on Tuesday as fresh U.S. sanctions on Russian oil disrupted exports.
+OPEC+ Plays the Waiting Game as Stock Builds Loom Large
+- This winters LNG markets are unlikely to replicate l… [+6512 chars]</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/3-natural-gas-stocks-gain-141400717.html</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Nilanjan Banerjee</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2025-10-20T14:14:00Z</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>3 Natural Gas Stocks to Gain From Rising Clean Energy Demand</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Rising global clean energy demand and higher gas prices position EQT, KMI and AR to capitalize on expanding natural gas opportunities.</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>To combat climate change, the world is gradually demanding cleaner fuel, which in turn is boosting demand for natural gas. The increasing number of data centers across the globe requires massive amou… [+2134 chars]</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>0.8834</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/wells-fargo-says-2-utility-110030108.html</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2025-10-30T11:00:30Z</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Wells Fargo Says These 2 Utility Stocks Are Among Its ‘Best Ideas’ for the Rest of 2025</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Utility stocks have long attracted investors for several reasons. They provide essential services – we can’t get along in the modern world without running...</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Utility stocks have long attracted investors for several reasons. They provide essential services we cant get along in the modern world without running water, reliable electricity, or safe supplies o… [+9632 chars]</t>
+        </is>
+      </c>
+      <c r="G328" t="n">
+        <v>0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/america-shale-strategy-powering-middle-000000733.html</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Simon Watkins</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2025-11-12T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>How America’s Shale Strategy Is Powering a New Middle East Energy Boom</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>U.S. shale oil and gas innovations have reversed the global energy power balance since the 1970s, now guiding Middle Eastern producers like Saudi Arabia and ...</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>The highly focused development of the U.S.’s shale oil and gas sectors from the early 2010s transformed it from one of the world’s biggest importers of both into one of its leading exporters of both.… [+8025 chars]</t>
+        </is>
+      </c>
+      <c r="G329" t="n">
+        <v>0.6115</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/earnings-live-circle-stock-slides-as-the-stablecoin-issuers-revenue-jumps-on-holding-stock-surges-132042367.html</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2025-11-12T13:20:42Z</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Earnings live: Circle stock slides as the stablecoin issuer's revenue jumps, On Holding stock surges</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>The third quarter earnings season has been mostly positive, with most of the reports in the rearview mirror.</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>The greater part of third quarter earnings results are in the rearview mirror, though investors this week are looking to reports from The Walt Disney Company (DIS) and Alibaba (BABA).
+So far, the Q3… [+18500 chars]</t>
+        </is>
+      </c>
+      <c r="G330" t="n">
+        <v>0.3612</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oneok-oke-reports-significant-growth-010214564.html</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:02:14Z</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ONEOK (OKE) Reports Significant Growth in Q3 Reports</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>ONEOK, Inc. (NYSE:OKE) is included among the 11 Best High Yield Energy Stocks to Buy Now. ONEOK, Inc. (NYSE:OKE) is one of the largest diversified energy...</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>ONEOK, Inc. (NYSE:OKE) is included among the 11 Best High Yield Energy Stocks to Buy Now.
+ONEOK (OKE) Reports Significant Growth in Q3 Reports
+ONEOK, Inc. (NYSE:OKE) is one of the largest diversifi… [+1257 chars]</t>
+        </is>
+      </c>
+      <c r="G331" t="n">
+        <v>0.9201</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/patterson-uti-energy-pten-gets-010228363.html</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2025-11-04T01:02:28Z</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Patterson-UTI Energy (PTEN) Gets Bullish Stance From Analyst Following Q3 Results</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Patterson-UTI Energy, Inc. (NASDAQ:PTEN) is included among the 11 Best High Yield Energy Stocks to Buy Now. Patterson-UTI Energy, Inc. (NASDAQ:PTEN) is a...</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Patterson-UTI Energy, Inc. (NASDAQ:PTEN) is included among the 11 Best High Yield Energy Stocks to Buy Now.
+Patterson-UTI Energy (PTEN) Gets Bullish Stance From Analyst Following Q3 Results
+Patters… [+1393 chars]</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>0.891</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/lng_sentiment_score_.xlsx
+++ b/data/lng_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G332"/>
+  <dimension ref="A1:G404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12156,6 +12156,2540 @@
         <v>0.891</v>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/articles/us-senator-calls-insider-trading-120003242.html</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Nina Lakhani and Joseph Gedeon</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2025-12-10T12:00:03Z</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>US senator calls for insider trading inquiry over Trump donors buying $12m worth of shares</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Co-chairs of LNG firm, who bought stock worth almost $12m each after meeting with Trump officials, deny wrongdoing</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>A senior Democratic senator is calling for an investigation into potential insider trading by fossil-fuel billionaires close to the Trump administration, after a Guardian investigation raised questio… [+2959 chars]</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>0.4767</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/3-oil-pipeline-stocks-solid-131200974.html</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Nilanjan Banerjee</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2025-12-09T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>3 Oil Pipeline Stocks With Solid Potential Amid Industry Strength</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Midstream players will secure additional cashflows from rising clean energy demand from data centers, which brightens the outlook for the Zacks Oil and Gas -...</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Unlike the upstream players, the business model of midstream companies is less vulnerable to the volatility in oil and natural gas prices. Importantly, rising clean energy demand from the data center… [+6313 chars]</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>0.8832</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/cheniere-energy-lng-falls-lng-111119393.html</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2025-12-12T11:11:19Z</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Cheniere Energy (LNG) Falls as LNG Stocks Come Under Pressure</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>The share price of Cheniere Energy, Inc. (NYSE:LNG) fell by 7.46% between December 3 and December 10, 2025, putting it among the Energy Stocks that Lost the ...</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>The share price of Cheniere Energy, Inc. (NYSE:LNG) fell by 7.46% between December 3 and December 10, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Cheniere Energy (LNG) Fal… [+1716 chars]</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>0.6249</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/3-high-yield-oil-stocks-154600772.html</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Nilanjan Choudhury</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2025-12-11T15:46:00Z</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>3 High-Yield Oil Stocks for Stable Income in a Bearish Market</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>CNQ, CVX and KMI offer yields over 4% and stable cash flow - key strengths in a bearish oil market heading into 2026.</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Oil markets are entering 2026 with rising inventories and weaker demand growth, creating a challenging backdrop for crude prices. Forecasts call for Brent and WTI to fall below $60 per barrel as a gl… [+5188 chars]</t>
+        </is>
+      </c>
+      <c r="G336" t="n">
+        <v>-0.128</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eni-secures-10-lng-deal-002004781.html</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2025-12-05T00:20:04Z</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Eni Secures 10-Year LNG Deal With Thailand’s Gulf Development Company</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Eni signs a decade-long LNG supply deal with Thailand’s Gulf Development, expanding its Asian footprint.</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Eni has strengthened its push into Asian LNG markets with a new 10-year sales agreement that will deliver 0.8 million tons per annum of LNG to Thailand’s Gulf Development Company. Deliveries will beg… [+1897 chars]</t>
+        </is>
+      </c>
+      <c r="G337" t="n">
+        <v>0.8074</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-seals-20-lng-010426769.html</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2025-11-26T01:04:26Z</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Venture Global Seals 20-Year LNG Supply Deal With Tokyo Gas</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Venture Global signs a long-term LNG supply agreement with Tokyo Gas for deliveries starting in 2030.</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Venture Global has agreed to supply Tokyo Gas with 1 MTPA of LNG for 20 years under a new sales and purchase agreement.
+Venture Global and Tokyo Gas have entered into a 20-year LNG Sales and Purchas… [+2225 chars]</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>0.6486</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/china-lng-imports-fall-13th-072843351.html</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2025-11-25T07:28:43Z</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>China’s LNG Imports Fall for 13th Straight Month as Domestic Output Surges</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>China’s LNG imports are falling for the 13th consecutive month as rising domestic gas production, full storage, tariffs, and increased Russian pipeline...</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>China’s imports of liquefied natural gas are set to decline for the 13th month in a row in November amid higher domestic production and pipeline imports, Bloomberg has reported, citing Kpler data.
+T… [+2145 chars]</t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>0.5266999999999999</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-accuses-shell-waging-073000286.html</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2025-11-26T07:30:00Z</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Venture Global Accuses Shell of Waging a Campaign to Damage Its Business</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Venture Global has accused Shell of running a three-year campaign to damage its reputation amid a continuing legal battle over LNG contracts tied to the...</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Venture Global has accused Shell of trying to damage its business by waging a “campaign” against it over the past three years, the Financial Times has reported, citing an internal message that Ventur… [+2296 chars]</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>-0.875</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/australia-mandate-lng-export-curbs-064441662.html</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2025-12-22T06:44:41Z</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Australia to Mandate LNG Export Curbs to Ensure Local Supply</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Australia plans to mandate that LNG producers reserve up to a quarter of output for domestic use from 2027, intensifying tensions with industry as the...</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Australia’s government is set to impose mandates on LNG producers in the country to set aside a certain percentage of their output for the domestic market to avoid shortages, despite industry opposit… [+2363 chars]</t>
+        </is>
+      </c>
+      <c r="G341" t="n">
+        <v>-0.0772</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/america-lng-boom-spike-power-200000636.html</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Leonard Hyman &amp; William Tilles</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2025-12-09T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>America’s LNG Boom Is About to Spike Your Power Bill</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>U.S. households and industries will face higher, more volatile gas and electricity prices.</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>The US is the world’s largest exporter of LNG. And efforts are apace to further increase that export capacity. As the US exports LNG at an increasing rate, this implies good news and bad news. The go… [+5177 chars]</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>0.1779</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_3ac4a3ed-785b-4eca-8833-60b76ccb1b82</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2025-12-11T09:23:14Z</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>EnerMech secures pre-commissioning contract for Pluto LNG 2 development</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 241 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G343" t="n">
+        <v>0.7003</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-strikes-back-shell-064500627.html</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2025-12-10T06:45:00Z</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Venture Global Strikes Back at Shell in LNG Arbitration Case</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Shell has appealed its arbitration loss against Venture Global, which maintains that the supermajor has provided no evidence of wrongdoing or contractual...</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Venture Global has claimed Shell has no evidence of Venture Global being involved in any wrongdoing, following the supermajor’s submission of an appeal to an earlier court ruling, in which the court … [+2461 chars]</t>
+        </is>
+      </c>
+      <c r="G344" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/scotiabank-remains-cautious-cheniere-energy-130713097.html</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2025-11-25T13:07:13Z</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Scotiabank Remains Cautious on Cheniere Energy (LNG), Maintains Outperform Rating</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Cheniere Energy Inc. (NYSE:LNG) is one of the most profitable large cap stocks to buy right now. On November 13, Scotiabank analyst Brandon Bingham lowered...</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Cheniere Energy Inc. (NYSE:LNG) is one of the most profitable large cap stocks to buy right now. On November 13, Scotiabank analyst Brandon Bingham lowered the firms price target on Cheniere Energy t… [+2274 chars]</t>
+        </is>
+      </c>
+      <c r="G345" t="n">
+        <v>0.7645</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jim-cramer-highlights-cheniere-lng-173442948.html</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Syeda Seirut Javed</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2025-12-17T17:34:42Z</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Jim Cramer Highlights Cheniere (LNG) Energy Partners’ 6.27% Yield</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (NYSE:LNG) is one of the stocks that Jim Cramer shared his take on. During the lightning round, a caller asked for Cramer’s thoughts on...</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (NYSE:LNG) is one of the stocks that Jim Cramer shared his take on. During the lightning round, a caller asked for Cramers thoughts on the stock, and he commented:
+Well, what I… [+1559 chars]</t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/cheniere-energy-lng-down-more-120052542.html</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Talha Qureshi</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2025-12-18T12:00:52Z</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>​Cheniere Energy (LNG) Down More than 10.4% since Q3 Results, Here’s What Wall Street Thinks About the Stock</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>​Cheniere Energy, Inc. (NYSE:LNG) is one of the Undervalued Stocks with Biggest Upside Potential. The share price of Cheniere Energy, Inc. (NYSE:LNG) has...</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (NYSE:LNG) is one of the Undervalued Stocks with Biggest Upside Potential. The share price of Cheniere Energy, Inc. (NYSE:LNG) has decreased by more than 10.4% since the release… [+1828 chars]</t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>0.7579</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_03479393-0278-44f9-89c3-fdc23338fc13</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2025-11-28T02:41:58Z</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Citi Trims Price Target for Venture Global (VG) Amid a Shaky LNG Outlook</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 240 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>0.3818</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/fortress-energy-nfe-soars-following-200307889.html</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2025-12-08T20:03:07Z</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>New Fortress Energy (NFE) Soars Following Final Approval of Puerto Rico LNG Agreement</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>The share price of New Fortress Energy Inc. (NASDAQ:NFE) surged by 28.69% between November 28 and December 5, 2025, putting it among the Energy Stocks that...</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>The share price of New Fortress Energy Inc. (NASDAQ:NFE) surged by 28.69% between November 28 and December 5, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+New Fortress En… [+1464 chars]</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>0.9371</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bp-boss-became-most-powerful-111251163.html</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Keira Wright and Ruth Liao</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2025-12-18T11:12:51Z</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>How BP’s New Boss Became the Most Powerful Woman in Fossil Fuels</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>At a moment when oil executives are still being pressed to move away from hydrocarbons, she has a different argument: that the world is nowhere near done...</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Company filings
+(Bloomberg) -- Meg ONeills rapid rise to the top of one of the worlds biggest fossil-fuel companies has been unencumbered by doubt. At a moment when oil executives are still being pr… [+8020 chars]</t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>0.3384</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jim-cramer-believes-venture-global-064302708.html</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Syeda Seirut Javed</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2025-11-29T06:43:02Z</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Jim Cramer Believes Venture Global “Has Been Very Disappointing”</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the stocks that received Jim Cramer’s latest comments. Cramer called the stock’s price action “disastrous,” as he...</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the stocks that received Jim Cramers latest comments. Cramer called the stocks price action disastrous, as he said:
+The quality of some of this years largest… [+1664 chars]</t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>-0.5994</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ceasefire-speculation-tests-oil-floor-160000514.html</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2025-11-25T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Ceasefire Speculation Tests Oil’s Floor</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Media reports that the Trump administration is inching ever closer to a comprehensive peace deal between Russia and Ukraine has exerted additional pressure...</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Oil fell 2.5% on Tuesday morning following reports that Ukraine has mostly agreed to a peace deal with the U.S.
+European Gas Prices Chill at Lowest Levels Since May 2024
+- European gas prices have … [+6550 chars]</t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-rise-as-surprise-adp-jobs-decline-reinforces-fed-rate-cut-bets-000151602.html</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2025-12-03T00:01:51Z</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as surprise ADP jobs decline reinforces Fed rate cut bets</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Doubts over AI demand put pressure on tech and a surprise fall in private-sector employment revealed cracks in the job market.</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>US stocks shook off early losses on Wednesday as a surprise decline in private-sector employment revealed cracks in the job market, but also reinforced bets on a Fed rate cut next week.
+The Dow Jone… [+14393 chars]</t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>-0.4854</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-rise-as-weak-adp-jobs-data-reinforces-growing-fed-rate-cut-bets-210358240.html</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2025-12-03T21:03:58Z</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as weak ADP jobs data reinforces growing Fed rate cut bets</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Doubts over AI demand put pressure on tech and a surprise fall in private-sector employment revealed cracks in the job market.</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>US stocks edged up on Wednesday as a surprise decline in private-sector employment revealed cracks in the job market, but also reinforced bets on a Fed rate cut next week.
+The Dow Jones Industrial A… [+15161 chars]</t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>-0.5023</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-bofa-lowered-pt-venture-120049129.html</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Talha Qureshi</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2025-12-18T12:00:49Z</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Here’s Why BofA Lowered the PT on Venture Global (VG)</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>​Venture Global, Inc. (NYSE:VG) is one of the Undervalued Stocks with Biggest Upside Potential. On December 10, Jean Ann Salisbury from the Bank of America...</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the Undervalued Stocks with Biggest Upside Potential. On December 10, Jean Ann Salisbury from the Bank of America Securities reiterated a Buy rating on Ventur… [+2033 chars]</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>0.1779</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-vg-enters-20-165758442.html</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Talha Qureshi</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2025-11-28T16:57:58Z</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Venture Global (VG) Enters a 20-Year Sale and Purchase Agreement with Tokyo Gas</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>​Venture Global, Inc. (NYSE:VG) is one of the Under-the-Radar Stocks to Buy with Massive Upside Heading into 2026. On November 25, Venture Global, Inc...</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) is one of the Under-the-Radar Stocks to Buy with Massive Upside Heading into 2026. On November 25, Venture Global, Inc. (NYSE:VG) announced a 20-year sale and purchase … [+1815 chars]</t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>0.4939</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/china-lng-slowdown-set-reshape-093000885.html</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2025-11-27T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>China’s LNG Slowdown Is Set to Reshape the Global Gas Trade</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>China’s LNG demand is set to fall 5% this year as pipeline imports and domestic production rise, pushing Japan back into the top spot for global LNG imports.</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>China’s demand for liquefied natural gas is on course for yet another annual decline this year, estimates from BloombergNEF suggest. The outlet expects Chinese LNG demand to be 5% weaker this year th… [+2233 chars]</t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-vg-posts-strong-063800558.html</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Sheryar Siddiq</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2025-12-03T06:38:00Z</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Venture Global (VG) Posts Strong Q3 EBITDA, Exceeding Analyst Estimates</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) ranks among the best energy stocks with huge upside potential. Goldman Sachs affirmed its Buy rating and $17.50 price target...</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Venture Global, Inc. (NYSE:VG) ranks among the best energy stocks with huge upside potential. Goldman Sachs affirmed its Buy rating and $17.50 price target for Venture Global, Inc. (NYSE:VG) on Novem… [+1609 chars]</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>0.8979</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-futures-tick-up-as-nvidia-jumps-ahead-of-fed-meeting-kickoff-233039719.html</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2025-12-08T23:30:39Z</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures tick up as Nvidia jumps ahead of Fed meeting kickoff</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>US stock futures inched up as Nvidia and the Fed dominate headlines in a busy week.</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Natural gas (NG=F) prices spent Monday in free fall, tumbling by more than 7.9% to drop back below the $5 mark.
+After a cold shock last week that saw prices jump above $5, a mark not seen since Dece… [+1487 chars]</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/europe-soft-gas-prices-put-000000085.html</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2025-12-08T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Europe’s Soft Gas Prices Put the Squeeze on U.S. LNG Traders</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>U.S. LNG exports are hitting record levels, but rising domestic gas prices are squeezing exporter margins.</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>U.S. exports of liquefied natural gas have been on a record-breaking streak this year, on track to book a 40% annual surge in November, thanks to strong European demand. There is just one problem: th… [+5468 chars]</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>0.6705</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eni-signs-10-lng-supply-140000869.html</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2025-12-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Eni Signs 10-Year LNG Supply Deal With Turkey's BOTAS Starting 2028</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Eni has secured a decade-long LNG sales agreement with Turkey’s state energy company BOTAS</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Eni has signed its first long-term LNG sales agreement with Turkey’s state-owned pipeline and gas company BOTA?, securing a decade of deliveries starting in 2028 as the Italian energy major continues… [+2292 chars]</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>0.765</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/petrochina-pipechina-launch-3-6-184018983.html</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2025-11-27T18:40:18Z</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>PetroChina and PipeChina Launch $3.6 Billion Gas Storage Joint Ventures</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>China’s PetroChina and state-owned pipeline operator PipeChina have jointly established two major gas storage companies</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>China’s PetroChina and state-owned pipeline operator PipeChina have jointly established two major gas storage companies, part of Beijing’s broader effort to expand natural gas capacity and stabilize … [+2562 chars]</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>0.5859</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/mizuho-upgrades-eqt-corp-eqt-195257372.html</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2025-12-19T19:52:57Z</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Mizuho Upgrades EQT Corp. (EQT) Outlook Citing Long-Term Value Despite Market Headwinds</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>EQT Corporation (NYSE:EQT) is one of the most profitable value stocks to invest in right now. On December 12, Mizuho raised the firm’s price target on EQT...</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>EQT Corporation (NYSE:EQT) is one of the most profitable value stocks to invest in right now. On December 12, Mizuho raised the firms price target on EQT Corporation to $68 from $60 and maintained an… [+2211 chars]</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>0.8058999999999999</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/most-boring-oil-month-years-150000584.html</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2025-12-02T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>The Most Boring Oil Month in Years Sets the Stage for a High-Stakes December</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>After a month where every geopolitical bet fizzled, the oil market enters December searching for its next catalyst.</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>After a month where every geopolitical bet fizzled, the oil market enters December searching for its next catalyst.
+2026 Forecasts Slide to $62 as Oversupply Clouds Outlook
+- The oil markets are in… [+7123 chars]</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>-0.3804</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/europe-locks-endgame-russian-gas-230000396.html</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Simon Watkins</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2025-12-09T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Europe Locks In Endgame for Russian Gas And Oil</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Sanctions pressure is escalating, hitting Russia’s LNG sector, shadow fleet, and—crucially—its top oil companies Rosneft and Lukoil.</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>The European Union (E.U.) of 27 member countries will “never go back to our dangerous dependence on Russia”, said Dan Jørgensen, European Commissioner (E.C.) for Energy last week. “We will never go b… [+9627 chars]</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/challenging-volatile-u-shale-150000249.html</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Rystad Energy</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2025-12-12T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>A Challenging and Volatile Year for U.S. Shale</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>A volatile 2025 left U.S. onshore operators navigating weak oil prices, structurally stronger gas fundamentals, tightening LNG economics, rising project...</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>The US shale exploration and production (E&amp;amp;P) and Lower 48 midstream sectors experienced a volatile and challenging 2025, likely a far cry from what operators envisioned this time last year as th… [+7815 chars]</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>-0.296</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/surge-natural-gas-prices-sets-220000007.html</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2025-12-07T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Surge in Natural Gas Prices Sets The Stage for Coal Comeback</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Soaring U.S. natural gas prices—driven by extreme cold and record LNG exports—have made coal a cheaper option for power generation.</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>As U.S. natural gas prices jumped to a three-year high, coal has become a cheaper power-generating fuel for utilities, which are set to run coal-fired generators harder this winter.
+U.S. benchmark n… [+4680 chars]</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_feefef4c-6cab-47a1-aaf9-d7af31239d9c</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2025-12-09T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Qatar Flags Post-2035 LNG Crunch as AI Demand Accelerates</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 241 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/totalenergies-clarifies-financing-shift-mozambique-074500636.html</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2025-12-03T07:45:00Z</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>TotalEnergies Clarifies Financing Shift for Mozambique LNG Project</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>TotalEnergies says partners will replace withdrawn UK and Dutch export credit support with extra equity.</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>TotalEnergies has moved to clarify the financing structure behind the long-delayed Mozambique LNG development after the UK and Dutch governments disclosed that their export credit agencies would no l… [+2738 chars]</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>0.3182</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/60-oil-no-longer-floor-160000123.html</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2025-12-19T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$60 Oil Is No Longer a Floor</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Brent is clinging to $60 per barrel, but markets have become even less sensitive to geopolitical risk.</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Brent is clinging to $60 per barrel, but markets have become even less sensitive to geopolitical risk.
+Friday, December 19, 2025 
+Things are not looking good for oil, with Trumps belligerent rhetor… [+5013 chars]</t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>-0.7476</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/lvs-advisory-discussion-growth-portfolio-123929502.html</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Soumya Eswaran</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2025-12-09T12:39:29Z</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>LVS Advisory’s Discussion on its Growth Portfolio’s investment: Golar LNG (GLNG)</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>LVS Advisory, a New York City-based full-service investment firm, recently released its third-quarter 2025 investor letter. A copy of the letter can be...</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>LVS Advisory, a New York City-based full-service investment firm, recently released its third-quarter 2025 investor letter. A copy of the letter can be downloaded here. The LVS Growth Portfolio gaine… [+2793 chars]</t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>0.6369</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/conocophillips-cop-inks-mou-pursue-111610821.html</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2025-11-27T11:16:10Z</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (COP) Inks MOU to Pursue Natural Gas Opportunities in Syria</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is an affordable blue-chip stock to buy. On November 18, ConocoPhillips (NYSE:COP), in partnership with Novatera and Syrian...</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is an affordable blue-chip stock to buy. On November 18, ConocoPhillips (NYSE:COP), in partnership with Novatera and Syrian Petroleum Company, inked a memorandum of understa… [+1759 chars]</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>0.6249</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/tamboran-resources-tbn-initiated-analyst-200315216.html</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2025-12-08T20:03:15Z</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Tamboran Resources (TBN) Initiated by Analyst with a $35 Price Target</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>The share price of Tamboran Resources Corporation (NYSE:TBN) surged by 9.96% between November 28 and December 5, 2025, putting it among the Energy Stocks...</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>The share price of Tamboran Resources Corporation (NYSE:TBN) surged by 9.96% between November 28 and December 5, 2025, putting it among the Energy Stocks that Gained the Most This Week.
+Tamboran Res… [+1566 chars]</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>0.7096</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/ubs-cautious-conocophillips-cop-amid-130708132.html</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2025-11-25T13:07:08Z</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>UBS Cautious on ConocoPhillips (COP) Amid Increased Willow Project Cost Estimates, Maintains ‘Buy’ Rating</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is one of the most undervalued NYSE stocks to buy right now. On November 12, UBS lowered the firm’s price target on ConocoPhillips ...</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>ConocoPhillips (NYSE:COP) is one of the most undervalued NYSE stocks to buy right now. On November 12, UBS lowered the firms price target on ConocoPhillips to $117 from $122 and kept a Buy rating on … [+1738 chars]</t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>0.0516</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/goldman-sachs-cuts-cheniere-energy-111613503.html</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2025-11-27T11:16:13Z</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Goldman Sachs Cuts Cheniere Energy, Inc. (LNG) Price Target on Soft Q3 Results but Asserts Buy Rating</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Cheniere Energy Inc. (NYSE:LNG) is an affordable blue-chip stock to buy. On November 3, Goldman Sachs reiterated a Buy rating on the stock but cut the price ...</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Cheniere Energy Inc. (NYSE:LNG) is an affordable blue-chip stock to buy. On November 3, Goldman Sachs reiterated a Buy rating on the stock but cut the price target to $275 from $2780. The price targe… [+1729 chars]</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>-0.0129</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-vg-continued-fall-182900591.html</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2025-12-05T18:29:00Z</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Venture Global (VG) Continued to Fall Following Price Target Cuts</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>The share price of Venture Global, Inc. (NYSE:VG) fell by 3.37% between November 26 and December 3, 2025, putting it among the Energy Stocks that Lost the...</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>The share price of Venture Global, Inc. (NYSE:VG) fell by 3.37% between November 26 and December 3, 2025, putting it among the Energy Stocks that Lost the Most This Week.
+Venture Global (VG) Continu… [+1536 chars]</t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>-0.0516</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-tanker-rates-skyrocket-467-110000581.html</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2025-12-11T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Oil Tanker Rates Skyrocket 467%</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>A shortage of supertankers is tightening the market and causing oil tanker charter rates to surge by 467% as new vessels race empty to load crude amid rising...</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>The supertanker market has tightened this year as crude supply from OPEC+ and the Americas rises and vessels make increasingly longer trips. So much has the market tightened that several new-built ve… [+2513 chars]</t>
+        </is>
+      </c>
+      <c r="G377" t="n">
+        <v>-0.5719</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/eni-targets-frontier-potential-uruguay-110000986.html</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2025-11-26T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Eni Targets Frontier Potential in Uruguay With Block OFF-5 Entry</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Eni has agreed to buy 50% of Uruguay’s deepwater Block OFF-5 from YPF, taking over operatorship to expand its high-impact exploration portfolio.</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Eni has signed a deal to acquire a 50% interest and operatorship of the offshore exploration Block OFF-5 in Uruguay from Argentina’s YPF, marking a fresh push into one of the Atlantic Margin’s least … [+2367 chars]</t>
+        </is>
+      </c>
+      <c r="G378" t="n">
+        <v>0.1027</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-sinks-despite-rate-cuts-153000094.html</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2025-12-12T15:30:00Z</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Oil Sinks Despite Rate Cuts and Tanker Seizures</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Oil sentiment has turned sour despite a Fed rate cut and the Trump administration’s aggressive tanker seizures.</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Oil sentiment has turned sour despite a Fed rate cut and the Trump administrations aggressive tanker seizures.
+Friday, December 12, 2025 
+The US Federal Reserve has lowered the federal funds rate t… [+5200 chars]</t>
+        </is>
+      </c>
+      <c r="G379" t="n">
+        <v>0.1536</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/australian-state-launches-first-gas-081500376.html</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2025-12-10T08:15:00Z</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Australian State Launches First Gas Tender in 7 Years</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Victoria has launched its first gas exploration tender since 2018 to counter a projected supply deficit despite long-term efforts to curb hydrocarbon use.</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>The state of Victoria is tendering gas exploration licenses for the first time since 2018 in a bid to avoid a shortage, despite efforts to reduce the consumption of hydrocarbons.
+In an announcement … [+2370 chars]</t>
+        </is>
+      </c>
+      <c r="G380" t="n">
+        <v>-0.1779</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-holds-gains-natural-gas-160000619.html</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2025-11-28T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Oil Holds Gains, Natural Gas Rockets as OPEC+ Meeting Nears</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>As Russia-Ukraine peace talks drag on, dampening last week’s hopes that a swift resolution could be around the corner, ICE Brent has settled comfortably...</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Crude oil is holding gains ahead of Sunday's OPEC+ meeting, while U.S. natural gas prices have spiked on the news of a new U.S. LNG export record.
+Friday, November 28, 2025
+As Russia-Ukraine peace … [+5215 chars]</t>
+        </is>
+      </c>
+      <c r="G381" t="n">
+        <v>0.8225</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/totalenergies-partners-japanese-giants-u-130000865.html</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2025-12-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>TotalEnergies Partners with Japanese Giants for U.S. Synthetic Gas Project</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>TotalEnergies, TES, and Japanese firms Osaka Gas, Toho Gas, and ITOCHU are partnering to develop the Live Oak project in Nebraska to produce electric natural...</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>TotalEnergies is partnering with several Japanese firms to develop the Live Oak project in Nebraska—a facility to produce electric natural gas (e-NG), synthetic gas produced from renewable hydrogen a… [+2486 chars]</t>
+        </is>
+      </c>
+      <c r="G382" t="n">
+        <v>0.3612</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/venture-global-vg-falls-nearly-160131875.html</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Angelica Ballesteros</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2025-12-02T16:01:31Z</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Venture Global (VG) Falls to Nearly 52-Week Low. Here’s What Dragged the Sentiment</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>We recently published 10 Stocks Already Hurting in December. Venture Global Inc. (NYSE:VG) is one of the top performers on Monday. Venture Global fell hard...</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>We recently published 10 Stocks Already Hurting in December. Venture Global Inc. (NYSE:VG) is one of the top performers on Monday.
+Venture Global fell hard on Monday to nearly hit its 52-week low, a… [+2097 chars]</t>
+        </is>
+      </c>
+      <c r="G383" t="n">
+        <v>-0.6908</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/fossil-fuel-billionaires-bought-millions-120021744.html</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Andy Rowell and Nina Lakhani</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2025-12-04T12:00:21Z</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Fossil-fuel billionaires bought up millions of shares after meeting with top Trump officials</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Co-founders’ acquisition of Venture Global shares before key permit granted draws scrutiny as pair deny wrongdoing</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Robert Pender, one of the co-founders of Venture Global, speaks at the CERAWeek conference in Houston in March 2019.Photograph: F Carter/Bloomberg via Getty Images
+Two fossil-fuel billionaires with … [+6902 chars]</t>
+        </is>
+      </c>
+      <c r="G384" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-trump-tariffs-hurt-drillers-150000712.html</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Robert Rapier</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2025-11-25T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Why Trump’s Tariffs Hurt Drillers More Than Refiners</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Trump’s second-term tariff strategy shields crude imports while driving up steel and equipment costs across the oil and gas value chain, reshaping project...</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>President Trump’s tariff strategy in his second term has touched almost every corner of the economy, but few sectors have felt the effects as unevenly as oil and gas. The administration has chosen no… [+7165 chars]</t>
+        </is>
+      </c>
+      <c r="G385" t="n">
+        <v>-0.296</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bofa-remains-bullish-chevron-corporation-134202363.html</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Fatima Gulzar</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2025-12-15T13:42:02Z</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>BofA Remains Bullish On Chevron Corporation (CVX)</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is among the 12 Best Performing Dow Stocks in 2025. TheFly reported on December 11, 2025, that BofA reduced its price goal for...</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Chevron Corporation (NYSE:CVX) is among the 12 Best Performing Dow Stocks in 2025. 
+BofA Remains Bullish On Chevron Corporation (CVX)
+TheFly reported on December 11, 2025, that BofA reduced its pri… [+1843 chars]</t>
+        </is>
+      </c>
+      <c r="G386" t="n">
+        <v>0.6369</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/uk-risks-gas-shortages-2030s-110000487.html</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2025-11-27T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>UK Risks Gas Shortages in 2030s as Domestic Output Plunges</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>A new NESO assessment warns that the UK could face emerging gas supply risks in the 2030s as domestic production collapses and dependence on imports grows...</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Britain could face emerging risks to natural gas supply in the 2030s as a freefall in domestic production makes it increasingly dependent on imports, the National Energy System Operator (NESO) has wa… [+2964 chars]</t>
+        </is>
+      </c>
+      <c r="G387" t="n">
+        <v>-0.0516</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/totalenergies-partners-advance-nebraska-e-103000045.html</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2025-12-02T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>TotalEnergies and Partners Advance Nebraska e-NG Project</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>TotalEnergies, TES, and three major Japanese gas players have formalized a joint development deal to advance the Live Oak e-NG project in Nebraska, targeting...</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>TotalEnergies, TES, and three Japanese gas companies have signed a development agreement for the Live Oak e-NG project in Nebraska, targeting commercial operations by 2030.
+The agreement brings in O… [+3122 chars]</t>
+        </is>
+      </c>
+      <c r="G388" t="n">
+        <v>0.7506</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/nigeria-namibia-africa-energy-revival-000000579.html</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2025-12-04T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>From Nigeria to Namibia, Africa’s Energy Revival Draws a Flood of New Capital</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Upstream spending is expected to reach $41 billion in 2026 as countries like Nigeria, Angola, Senegal, Côte d’Ivoire, and Namibia court supermajors.</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Many of the resource-rich countries in Africa have intensified efforts to become more attractive for exploration and production (E&amp;amp;P) investment. Reforms in licensing rounds, production sharing c… [+5906 chars]</t>
+        </is>
+      </c>
+      <c r="G389" t="n">
+        <v>0.8502999999999999</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-rise-as-fed-meeting-kicks-off-jolts-data-shows-openings-rose-143633201.html</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2025-12-09T14:36:33Z</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as Fed meeting kicks off, JOLTS data shows openings rose</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Wall Street is looking to the Fed policy meeting starting today for clues to the odds of more rate cuts in 2026.</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>US stocks turned into the green Tuesday morning as the Federal Reserve's December policy meeting kicked off and federal data showed job openings unexpectedly ticked higher even as layoffs jumped.
+Th… [+13935 chars]</t>
+        </is>
+      </c>
+      <c r="G390" t="n">
+        <v>-0.4215</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-sp-500-nasdaq-trade-mixed-as-fed-rate-meeting-kicks-off-143633994.html</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2025-12-08T23:30:39Z</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures in holding pattern as Fed meeting kicks off</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Wall Street is looking to the Fed policy meeting starting today for clues to the odds of more rate cuts in 2026.</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Us stocks were mixed as the tech sector turned into the red on Tuesday morning and the Federal Reserve's December policy meeting began, with investors convinced of a rate cut this week turning their … [+10762 chars]</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>0.1531</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/woodside-names-liz-westcott-acting-091529063.html</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2025-12-18T09:15:29Z</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Woodside Names Liz Westcott Acting CEO as Meg O’Neill Heads to BP</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Woodside Energy has appointed Liz Westcott as Acting CEO after Meg O’Neill resigned to take the top job at bp.</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Woodside Energy has moved quickly to stabilize leadership following the resignation of CEO and Managing Director Meg O’Neill, who is departing to become chief executive of bp p.l.c. The Australian oi… [+3181 chars]</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>-0.0258</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-markets-lackluster-amid-russia-230000354.html</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2025-11-27T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Oil Markets Lackluster Amid Russia Peace Deal, China’s Stockpiling</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>China continues aggressive stockpiling, importing over 11.4 mb/d of crude and adding roughly 1 mb/d to reserves in some months.</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Sentiment in oil markets remains overwhelmingly negative, driven by perceived market oversupply and negative global demand indicators. Brent crude for January delivery was trading at $63.10 per barre… [+5417 chars]</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>-0.8625</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/morning-bid-odd-jobs-bonds-123218003.html</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2025-12-04T12:32:18Z</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Morning Bid: Odd jobs and bonds</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>LONDON, Dec 4 () - By Marc Jones, global markets correspondent What matters in US and global markets today It appears the U. economy is experiencing some...</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>LONDON, Dec 4 (Reuters) - By Marc Jones, global markets correspondent
+What matters in US and global markets today
+It appears the U.S. economy is experiencing some pain and the dollar is among the a… [+5675 chars]</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>-0.6705</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-snap-higher-market-may-000000437.html</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2025-12-11T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Is Oil About to Snap Higher? The Market May Be Too Bearish</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Lower prices risk slowing U.S. shale and non-OPEC+ output, setting up the possibility that today’s glut becomes tomorrow’s crunch</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Rising oil supply amid tepid demand growth has prompted forecasters and analysts to predict a large surplus on the market going into 2026.
+All experts and investment banks estimate that the market i… [+4315 chars]</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/exxonmobil-bets-layered-tech-systems-020000689.html</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2025-12-12T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>ExxonMobil Bets on Layered Tech Systems to Reinvent Shale Economics</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>ExxonMobil is reshaping shale economics with 40+ “stackable technologies”.</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>ExxonMobil released its updated corporate plan on Tuesday, wherein it upgraded its 5-year outlook. Exxon expects earnings to increase by more than $14 billion at constant prices through 2030 from 202… [+5535 chars]</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>0.3182</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bofa-cautious-kbr-kbr-amid-132805088.html</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2025-11-25T13:28:05Z</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>BofA Cautious on KBR (KBR) Amid Macro Headwinds, Impending Business Split</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>KBR Inc. (NYSE:KBR) is one of the most undervalued NYSE stocks to buy right now. On November 13, BofA lowered the firm’s price target on KBR to $45 from $55 ...</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>KBR Inc. (NYSE:KBR) is one of the most undervalued NYSE stocks to buy right now. On November 13, BofA lowered the firms price target on KBR to $45 from $55 and kept a Neutral rating on the shares. Wh… [+1734 chars]</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>0.0772</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/westport-fuel-systems-inc-wprt-131606763.html</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2025-11-25T13:16:06Z</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Westport Fuel Systems Inc. (WPRT) is a Buy on Strategic Positioning and Growth Potential: H.C. Wainwright</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Westport Fuel Systems Inc. (NASDAQ:WPRT) is one of the Canadian penny stocks to buy right now. On November 12, H.C. Wainwright reiterated a Buy rating on...</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Westport Fuel Systems Inc. (NASDAQ:WPRT) is one of the Canadian penny stocks to buy right now. On November 12, H.C. Wainwright reiterated a Buy rating on Westport Fuel Systems Inc. (NASDAQ:WPRT) and … [+1837 chars]</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>0.3818</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/why-eqt-corporation-eqt-fell-125015551.html</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Soumya Eswaran</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2025-12-03T12:50:15Z</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Here’s Why EQT Corporation (EQT) Fell in Q3</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Scout Investments, Inc., an affiliate of Carillon Tower Advisers, recently released its third-quarter 2025 investor letter for “Carillon Scout Mid Cap Fund”....</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Scout Investments, Inc., an affiliate of Carillon Tower Advisers, recently released its third-quarter 2025 investor letter for Carillon Scout Mid Cap Fund. A copy of the letter can be downloaded here… [+2393 chars]</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/cpc-cuts-fail-lift-brent-161926076.html</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2025-12-05T16:19:26Z</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>CPC Cuts Fail to Lift Brent as Saudi Pricing Undercuts Rally</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Oil prices remained stuck in a narrow range this week, with Brent hovering around $63 per barrel.</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Oil prices remained stuck in a narrow range this week, with Brent hovering around $63 per barrel.
+Friday, December 05, 2025
+Oil prices remained rangebound this week, with ICE Brent still hovering a… [+4782 chars]</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>-0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/adnoc-approves-sweeping-150-billion-021149861.html</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2025-11-25T02:11:49Z</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>ADNOC Approves Sweeping $150 Billion Investment Plan</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>ADNOC has approved a sweeping US$150 billion investment plan for 2026–2030 to expand upstream capacity, accelerate gas development, scale downstream and...</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>ADNOC has unveiled a sweeping $150 billion investment plan for 2026–2030, marking one of the largest investment cycles in its history and reinforcing the UAE’s long-term commitment to oil, gas, and i… [+3114 chars]</t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>0.6486</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/gunvor-buccaneering-founder-hands-reins-114109578.html</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Archie Hunter, Lucia Kassai, Devika Krishna Kumar and Alex Longley</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2025-12-02T11:41:09Z</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Gunvor’s Buccaneering Founder Hands Reins to American Oil Trader</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>On Monday, the 72-year-old Swede announced an abrupt departure from the company he cofounded in a dramatic move to contain the fallout after the US Treasury ...</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Gary Pedersen
+(Bloomberg) -- Torbjörn Törnqvist spent three decades building Gunvor Group into one of the worlds largest energy traders from early days exporting fuel from post-Soviet Russia, to tod… [+8281 chars]</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>0.2732</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-rises-sp-500-and-nasdaq-under-pressure-as-key-adp-jobs-data-shows-weakness-000151158.html</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2025-12-03T00:01:51Z</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow rises, S&amp;P 500 and Nasdaq under pressure as key ADP jobs data shows weakness</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Doubts over AI demand put pressure on tech and a surprise fall in private-sector employment revealed cracks in the job market.</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>The Dow led diverging US stocks on Wednesday as doubts over AI demand put pressure on tech, and a surprise fall in private-sector employment revealed cracks in the job market.
+The Dow Jones Industri… [+12496 chars]</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>-0.7783</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/stock-market-today-dow-and-sp-500-rise-nasdaq-pares-losses-as-key-adp-jobs-data-shows-weakness-000151469.html</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Rian Howlett</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2025-12-03T00:01:51Z</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Stock market today: Dow and S&amp;P 500 rise, Nasdaq pares losses as key ADP jobs data shows weakness</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Doubts over AI demand put pressure on tech and a surprise fall in private-sector employment revealed cracks in the job market.</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>The Dow led diverging US stocks on Wednesday as doubts over AI demand put pressure on tech, and a surprise fall in private-sector employment revealed cracks in the job market.
+The Dow Jones Industri… [+13670 chars]</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>-0.8074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/lng_sentiment_score_.xlsx
+++ b/data/lng_sentiment_score_.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G404"/>
+  <dimension ref="A1:G449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14690,6 +14690,1479 @@
         <v>-0.8074</v>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_7fe1d955-b1f9-4aae-bdeb-392ed6189655</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2026-01-11T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>China’s Gas Growth Casts a Shadow over LNG Demand</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>0.6808</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_f8fce0a7-0aa0-4c8f-8f93-650d46f6f2a2</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2026-01-30T12:25:23Z</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Rising oil, gas and LNG demand draws global traders to India</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/vitol-extends-brunei-lng-supply-033411909.html</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2026-01-23T03:34:11Z</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Vitol Extends Brunei LNG Supply Deal Through 2031</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Brunei Energy Services &amp; Trading and Vitol have agreed to extend their LNG sales agreement, ensuring continued cargo deliveries into the next decade.</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Brunei Energy Services &amp;amp; Trading and global energy trader Vitol have extended their long-term liquefied natural gas Sale and Purchase Agreement, reinforcing a partnership first established in 202… [+2528 chars]</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>0.8555</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_36c2e889-511a-443c-b8f7-e688472fb166</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2026-01-15T07:43:45Z</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Saudi Aramco Signs Long-Term LNG Supply Agreement in Louisiana</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G408" t="n">
+        <v>0.7717000000000001</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_3ac47c5e-5853-4ab1-86db-2d694f5923a7</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2026-01-30T17:53:13Z</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Cheniere Energy (LNG) Declares Quarterly Dividend of $0.555 per Share</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>0.7783</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_3f30684b-968f-4d33-851f-2f97e276a91f</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2026-01-19T12:27:22Z</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Scotiabank Upgrades Cheniere Energy (LNG) to Outperform, Wolfe Research Raises PT</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>0.6808</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/apa-corp-apa-jumps-8-022326177.html</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Angelica Ballesteros</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2026-01-09T02:23:26Z</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>APA Corp (APA) Jumps 8.5% on LNG Demand Growth, Colder Season</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>We recently published Wall Street Can’t Keep up With These 10 Stocks on Fire. APA Corporation (NASDAQ:APA) was one of the top performers on Thursday. APA...</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>We recently published Wall Street Cant Keep up With These 10 Stocks on Fire. APA Corporation (NASDAQ:APA)  was one of the top performers on Thursday.
+APA Corporation (NASDAQ:APA) grew its share pric… [+2170 chars]</t>
+        </is>
+      </c>
+      <c r="G411" t="n">
+        <v>0.4019</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_c36749eb-bacb-4bf5-9431-69c29d83ece0</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2026-01-22T02:16:30Z</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Scotiabank Raises Enterprise Products (EPD) Target to $35 on Strong Power Demand and LNG Tailwinds</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>0.743</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_545c9f00-884b-4454-a270-ecff419dcf86</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2026-01-22T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Kinder Morgan Posts Record Earnings as LNG Demand Fuels Pipeline Growth</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G413" t="n">
+        <v>0.8316</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jefferies-cuts-cheniere-lng-target-233256037.html</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Vardah Gill</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2026-01-29T23:32:56Z</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Jefferies Cuts Cheniere (LNG) Target but Stays Constructive Ahead of Q4</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (NYSE:LNG) is included among the 13 Best February Dividend Stocks to Buy. Jefferies cut its price target on Cheniere Energy, Inc...</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (NYSE:LNG) is included among the 13 Best February Dividend Stocks to Buy.
+Jefferies Cuts Cheniere (LNG) Target but Stays Constructive Ahead of Q4
+Jefferies cut its price targe… [+2109 chars]</t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>0.5266999999999999</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/rbc-capital-trims-cheniere-energy-124608285.html</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Maham Fatima</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2026-01-31T12:46:08Z</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>RBC Capital Trims Cheniere Energy (LNG) PT to $271, Maintains Outperform Rating</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Cheniere Energy Inc. (NYSE:LNG) is one of the most undervalued large cap stocks to invest in now. On January 28, RBC Capital lowered its price target for...</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Cheniere Energy Inc. (NYSE:LNG) is one of the most undervalued large cap stocks to invest in now. On January 28, RBC Capital lowered its price target for Cheniere Energy to $271 from $282 while maint… [+1822 chars]</t>
+        </is>
+      </c>
+      <c r="G415" t="n">
+        <v>0.5859</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/russia-oil-flows-pivot-east-093000762.html</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2026-01-13T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Russia’s Oil Flows Pivot East as China Buys More and India Pulls Back</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Russia’s December oil exports surged on higher shipments to China while deliveries to India fell sharply, reflecting shifting trade patterns under sanctions ...</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Crude oil exports from Russia to China last month went up by 23% on the previous month, while exports to India declined by 29% on the month, Finnish Centre for Research on Energy and Clean Air said i… [+2209 chars]</t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>0.0258</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/golar-lng-limited-glng-bull-145635692.html</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Ricardo Pillai</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2026-01-15T14:56:35Z</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Golar LNG Limited (GLNG): A Bull Case Theory</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on Golar LNG Limited on X.com by justfactstruth. In this article, we will summarize the bulls’ thesis on GLNG. Golar LNG...</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>We came across a bullish thesis on Golar LNG Limited on X.com by justfactstruth. In this article, we will summarize the bulls thesis on GLNG. Golar LNG Limited's share was trading at $38.59 as of Jan… [+2538 chars]</t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>-0.1531</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/scotiabank-constructive-williams-companies-wmb-164232863.html</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Faheem Tahir</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2026-01-26T16:42:32Z</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Scotiabank Constructive on The Williams Companies (WMB) Amid Broader Reset of Energy Infrastructure Valuations</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>The Williams Companies, Inc. (NYSE:WMB) is included in our list of the best AI energy stocks to buy now. On January 16, 2026, The Williams Companies, Inc...</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>The Williams Companies, Inc. (NYSE:WMB) is included in our list of the best AI energy stocks to buy now.
+Scotiabank Constructive on The Williams Companies (WMB) Amid Broader Reset of Energy Infrastr… [+1974 chars]</t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>0.8591</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/adnoc-expects-oil-demand-stay-143000405.html</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:30:00Z</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>ADNOC Expects Oil Demand to Stay Above 100 Million Barrels a Day Through 2040</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>ADNOC CEO Sultan Al Jaber says global oil demand will remain above 100 million bpd through 2040, warning that underinvestment across all energy sources poses...</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Oil demand will stay above 100 million barrels per day (bpd) through 2040, the chief executive of Abu Dhabi National Oil Company (ADNOC) said on Tuesday, reiterating the need for investment in all fo… [+2223 chars]</t>
+        </is>
+      </c>
+      <c r="G419" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/oil-lng-too-much-supply-003000637.html</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Irina Slav</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2026-01-06T00:30:00Z</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>From Oil to LNG, Too Much Supply Is Still the Problem in 2026</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>New U.S. LNG export capacity is coming online just as European prices and margins weaken, raising the risk that exporters curb volumes if spreads narrow...</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Crude oil began trade this year with a dip, despite the news about U.S. strikes on Venezuela and the taking of President Nicolas Maduro to the U.S. Normally, such events would have pushed oil higher,… [+5594 chars]</t>
+        </is>
+      </c>
+      <c r="G420" t="n">
+        <v>-0.836</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_4b68199c-037b-4923-9640-9702f329e774</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2026-01-20T08:30:00Z</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>India Locks In Major LNG Supply Deal With Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>0.5423</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_2bc72b50-93e8-45bd-b50b-2cd42037395e</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2026-01-15T14:37:48Z</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (LNG): A Bull Case Theory</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G422" t="n">
+        <v>0.6808</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_11ee3f79-548b-4da0-bb53-d3ae7fe80f82</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2026-01-19T09:47:51Z</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Larsen &amp; Toubro unit wins Petronet LNG contract for Dahej complex</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G423" t="n">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/trumps-whiplash-iran-rhetoric-keeps-155200578.html</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2026-01-30T15:52:00Z</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Trump's Whiplash Iran Rhetoric Keeps Oil Bulls in Control</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Markets looked past rising supply as shifting U.S. rhetoric on Iran and ongoing weather-related disruptions kept risk premiums elevated</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Markets looked past rising supply as shifting U.S. rhetoric on Iran and ongoing weather-related disruptions kept risk premiums elevated.
+Friday, January 30, 2026 
+Trumps erratic rhetoric has been g… [+4896 chars]</t>
+        </is>
+      </c>
+      <c r="G424" t="n">
+        <v>-0.5423</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/mitsubishi-enters-u-shale-5-072032126.html</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2026-01-16T07:20:32Z</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Mitsubishi Enters U.S. Shale With $5.2 Billion Haynesville Gas Deal</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Mitsubishi Corporation is acquiring Aethon’s Haynesville shale gas business for $5.2 billion, marking its entry into U.S. shale gas and strengthening its...</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Mitsubishi Corporation has agreed to acquire Aethon’s Haynesville shale gas business in a transaction valued at approximately $5.2 billion, marking the Japanese conglomerate’s first direct entry into… [+3250 chars]</t>
+        </is>
+      </c>
+      <c r="G425" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_f698d4ac-cc4c-457b-9d34-35cb7c051b28</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2026-01-26T02:23:37Z</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Baker Hughes Posts Record Backlog as LNG and Power Orders Lift 2025 Results</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G426" t="n">
+        <v>0.5423</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_12d98227-6e6e-43c9-ada2-ba8402fb84e0</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2026-01-29T07:07:35Z</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Barclays Revises Cheniere Energy (LNG) Outlook Highlighting Strength in Natural Gas Market</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G427" t="n">
+        <v>0.8834</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/uae-150-billion-gas-bet-200000809.html</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Simon Watkins</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2026-01-07T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>The UAE’s $150 Billion Gas Bet Could Upend Global LNG Markets</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>The UAE plans to invest $150 billion in gas by 2030, boosting output by 50%, achieving gas self-sufficiency, while also creating a surplus to export.</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>There is a lot more to the UAE’s recently announced US$150 billion turbo-boost to its gas sector than meets the eye. It is true that it should deliver multiple economic benefits for the Middle Easter… [+7650 chars]</t>
+        </is>
+      </c>
+      <c r="G428" t="n">
+        <v>0.6597</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/novagold-resources-donlin-gold-llc-141249727.html</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Ali Hassan</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2026-01-14T14:12:49Z</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>NovaGold Resources’ Donlin Gold LLC Signs a Non-Binding Natural Gas LOI with Glenfarne Alaska LNG</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>NovaGold Resources Inc. (NYSE:NG) is one of the 10 Best Precious Metal Stocks to Buy After the U.S. Venezuela Mission. All five analysts covering NovaGold...</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>NovaGold Resources Inc. (NYSE:NG) is one of the 10Best Precious Metal Stocks to Buy After the U.S. Venezuela Mission.
+All five analysts covering NovaGold Resources Inc. (NYSE:NG) have rated it a Buy… [+2499 chars]</t>
+        </is>
+      </c>
+      <c r="G429" t="n">
+        <v>0.7351</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_14d685b6-1741-4f90-a6cf-8edabe939f5e</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2026-01-22T01:23:26Z</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Santos Delivers Strong Cash Flow as Barossa LNG Ships First Cargo</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and / or access information on a device (in other words, us… [+1046 chars]</t>
+        </is>
+      </c>
+      <c r="G430" t="n">
+        <v>0.7783</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_8659b031-9d35-44d1-9cd7-c1ab9dbe085a</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2026-01-09T02:40:45Z</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Venture Global (VG) Jumps 10% as LNG Demand Spikes Up in Winter</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>0.4588</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>https://consent.yahoo.com/v2/collectConsent?sessionId=1_cc-session_f137e4ef-f2b9-4707-acc2-c2cd52d51a3b</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2026-01-08T05:12:39Z</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Energy Transfer (ET) Halts the Development of Lake Charles LNG Facility</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>If you click 'Accept all', we and our partners, including 245 who are part of the IAB Transparency &amp;amp; Consent Framework, will also store and/or access information on a device (in other words, use … [+714 chars]</t>
+        </is>
+      </c>
+      <c r="G432" t="n">
+        <v>0.6808</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/shell-chemical-business-set-swing-110000771.html</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2026-01-08T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Shell Chemical Business Set to Swing to a Loss in Q4</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Shell anticipates its chemicals and products division will record a significant loss in the fourth quarter of 2025 due to a drop in chemicals margins and a...</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Shell expects its chemicals and products division to swing to a loss in the fourth quarter of 2025, on the back of lower chemicals margin compared to the previous quarter, the UK-based supermajor sai… [+2389 chars]</t>
+        </is>
+      </c>
+      <c r="G433" t="n">
+        <v>-0.7003</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/p-500-gains-may-slow-105903894.html</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2026-01-13T10:59:03Z</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 Gains May Slow in 2026 — but Raymond James Says These 2 Stocks Could Beat the Market</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>After posting a 16% gain last year, the S&amp;P 500 capped off its third straight year of double-digit returns. But can 2026 deliver another solid year for...</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>After posting a 16% gain last year, the S&amp;amp;P 500 capped off its third straight year of double-digit returns. But can 2026 deliver another solid year for equities, or is the market due for a cooldo… [+8095 chars]</t>
+        </is>
+      </c>
+      <c r="G434" t="n">
+        <v>0.8608</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/totalenergies-expects-strong-q4-refining-120000418.html</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2026-01-20T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>TotalEnergies Expects Strong Q4 Refining to Offset Lower Oil Prices</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>TotalEnergies predicts steady fourth-quarter cash flow, driven by stronger refining margins and increased oil and gas production which compensated for a...</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>TotalEnergies expects higher oil and gas production and stronger refining margins in the fourth quarter to have offset a drop of more than $10 per barrel in oil prices, the French supermajor said on … [+2718 chars]</t>
+        </is>
+      </c>
+      <c r="G435" t="n">
+        <v>0.3818</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jim-cramer-cheniere-energy-not-081647048.html</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Syeda Seirut Javed</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2026-01-09T08:16:47Z</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Jim Cramer on Cheniere Energy: “It’s Not My Favorite Right Here”</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (NYSE:LNG) is one of the stocks Jim Cramer shared his takes on. Noting that the stock has been sliding for nearly a year now, a caller ...</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Cheniere Energy, Inc. (NYSE:LNG) is one of the stocks Jim Cramer shared his takes on. Noting that the stock has been sliding for nearly a year now, a caller asked if it is a good time to invest in it… [+1390 chars]</t>
+        </is>
+      </c>
+      <c r="G436" t="n">
+        <v>0.7202</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/natural-gas-services-group-ngs-101633958.html</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Sultan Khalid</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2026-01-18T10:16:33Z</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Natural Gas Services Group (NGS) Downgraded to ‘Outperform’</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>The share price of Natural Gas Services Group, Inc. (NYSE:NGS) fell by 2.18% between January 9 and January 16, 2026, putting it among the Energy Stocks that ...</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>The share price of Natural Gas Services Group, Inc. (NYSE:NGS) fell by 2.18% between January 9 and January 16, 2026, putting it among the Energy Stocks that Lost the Most This Week.
+Natural Gas Serv… [+1348 chars]</t>
+        </is>
+      </c>
+      <c r="G437" t="n">
+        <v>0.8176</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/jim-cramer-says-navigator-holdings-175204273.html</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Syeda Seirut Javed</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2026-01-28T17:52:04Z</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Jim Cramer Says Navigator Holdings Is “Doing Well” But He Prefers Its Peers</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Navigator Holdings Ltd. (NYSE:NVGS) is one of the stocks Jim Cramer answered questions about. Inquiring about the stock, a caller mentioned that they have a ...</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Navigator Holdings Ltd. (NYSE:NVGS) is one of the stocks Jim Cramer answered questions about. Inquiring about the stock, a caller mentioned that they have a position in it, and Cramer commented:
+Loo… [+1072 chars]</t>
+        </is>
+      </c>
+      <c r="G438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/global-upstream-capex-set-fall-000000561.html</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Alex Kimani</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2026-01-12T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Global Upstream Capex Set To Fall Again In 2026 Amid Low Oil Prices</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Producers prioritize capital discipline amid sub-$60 oil prices, with cuts in North America and Europe offsetting higher spending in the Middle East and...</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Last year, upstream oil investment was projected to have declined 2.5% Y/Y to $420 billion after low oil prices put pressure on producers and slowed expansion plans. Companies across the industry con… [+5185 chars]</t>
+        </is>
+      </c>
+      <c r="G439" t="n">
+        <v>-0.6597</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/tengiz-disruption-lifts-brent-back-154500761.html</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2026-01-20T15:45:00Z</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Tengiz Disruption Lifts Brent Back to $65</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Oil markets are ignoring Trump’s Greenland drama as a fire at Kazakhstan’s giant Tengiz field tightens supply, lifting Brent back to $65.</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Oil markets are ignoring Trumps Greenland drama as a fire at Kazakhstans giant Tengiz field tightens supply, lifting Brent back to $65.
+China Embraces Dominant Power-Producer Role
+- With Chinas Nat… [+6505 chars]</t>
+        </is>
+      </c>
+      <c r="G440" t="n">
+        <v>-0.765</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/markets-price-chaos-oil-finds-154342248.html</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Tom Kool</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2026-01-13T15:43:42Z</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Markets Price Chaos as Oil Finds Its Footing</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Oil prices have rebounded sharply on geopolitical risk despite no meaningful supply losses.</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Oil prices have rebounded sharply on geopolitical risk despite no meaningful supply losses.
+Call Options Go Wild as Brent Traders Bet Big on Chaos
+- Iran protests and the increasing probability tha… [+6742 chars]</t>
+        </is>
+      </c>
+      <c r="G441" t="n">
+        <v>-0.9213</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/staatsolie-closes-2025-strong-note-172639912.html</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Charles Kennedy</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2026-01-15T17:26:39Z</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Staatsolie Closes 2025 on Strong Note, Looks Forward to Pivotal 2026</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Suriname’s oil and gas sector is entering a decisive phase in 2026 as major projects move from exploration and planning into execution and commercial...</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Suriname’s oil and gas sector is entering a decisive phase in 2026 as major projects move from exploration and planning into execution and commercial decision-making. With offshore developments advan… [+2431 chars]</t>
+        </is>
+      </c>
+      <c r="G442" t="n">
+        <v>0.7269</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/natural-gas-prices-soar-dangerous-211514211.html</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Julian Hast, Priscila Azevedo Rocha and Joe Wertz</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2026-01-21T21:15:14Z</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Natural Gas Prices Soar as Dangerous Freeze Takes Hold Across Massive Swath of the US</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>A storm will descend on the US starting Friday, plunging Texas into a deep freeze before threatening to dump snow on New York City and Boston.  The...</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Bloomberg
+(Bloomberg) -- US natural gas futures jumped more than 50% in two days, putting futures on track for their biggest weekly gain in more than three decades, as dangerously cold temperatures … [+6022 chars]</t>
+        </is>
+      </c>
+      <c r="G443" t="n">
+        <v>0.3612</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/iran-turmoil-resurrects-specter-critical-210000119.html</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2026-01-13T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Iran Turmoil Resurrects Specter of Critical Oil Lane Disruption</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>The Strait of Hormuz risk is back in focus, as escalation could threaten a route that carries about 20% of global oil supply—though a full closure remains...</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Oil prices haven’t had a breather since the year started as one geopolitical crisis has moved to another. Just a week after the U.S. intervention in Venezuela captured Nicolas Maduro, U.S. President … [+5603 chars]</t>
+        </is>
+      </c>
+      <c r="G444" t="n">
+        <v>-0.886</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/uk-north-sea-oil-enters-220000982.html</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Tsvetana Paraskova</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2026-01-06T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>UK North Sea Oil Enters Survival Mode as Investment Dries Up</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>UK North Sea oil and gas endured its toughest year in decades in 2025, with investment pulled back sharply and offshore exploration falling to zero.</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>The once-thriving UK North Sea oil and gas province survived 2025, the most difficult year since the 1960s when hydrocarbons were first discovered in the basin.
+Oil and gas production from the matur… [+6291 chars]</t>
+        </is>
+      </c>
+      <c r="G445" t="n">
+        <v>0.1298</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/earnings-live-unitedhealth-stock-falls-19-american-airlines-slides-texas-instruments-pops-logitech-edges-higher-213941564.html</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2026-01-27T21:39:41Z</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Earnings live: UnitedHealth stock falls 19%, American Airlines slides, Texas Instruments pops, Logitech edges higher</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>The fourth quarter earnings season kicks into high gear this week, with Big Tech results from Microsoft, Meta, Tesla, and Apple headlining the earnings...</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>The fourth quarter earnings season kicks into high gear this week, with Big Tech results from Microsoft (MSFT), Meta (META), Tesla (TSLA), and Apple (AAPL) headlining the earnings calendar.
+An optim… [+18769 chars]</t>
+        </is>
+      </c>
+      <c r="G446" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/earnings-live-baker-hughes-stock-rises-as-big-tech-earnings-come-into-view-133500361.html</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2026-01-26T13:35:00Z</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Earnings live: Baker Hughes stock rises as Big Tech earnings come into view</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>The fourth quarter earnings season kicks into high gear this week, with Big Tech results from Microsoft, Meta, Tesla, and Apple headlining the earnings...</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>The fourth quarter earnings season kicks into high gear this week, with Big Tech results from Microsoft (MSFT), Meta (META), Tesla (TSLA), and Apple (AAPL) headlining the earnings calendar.
+An optim… [+17929 chars]</t>
+        </is>
+      </c>
+      <c r="G447" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/iraq-biggest-geopolitical-pivot-years-160000851.html</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Simon Watkins</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2026-01-12T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Is Iraq About to Make Its Biggest Geopolitical Pivot in Years?</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>The shift could signal Iraq’s gradual pivot back toward the West, as U.S. and European energy investments anchor Baghdad’s interests away from Moscow...</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Following the Iraq Oil Ministry’s recent dispatch of exclusive invitations to several major U.S. energy firms to develop the country’s huge West Qurna 2 oilfield after the forced exit of Russian oil … [+8689 chars]</t>
+        </is>
+      </c>
+      <c r="G448" t="n">
+        <v>0.2263</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/live/earnings-live-unitedhealth-stock-tumbles-ups-and-general-motors-rise-130729919.html</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2026-01-27T13:07:29Z</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Earnings live: UnitedHealth stock tumbles, UPS and General Motors rise</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>The fourth quarter earnings season kicks into high gear this week, with Big Tech results from Microsoft, Meta, Tesla, and Apple headlining the earnings...</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>The fourth quarter earnings season kicks into high gear this week, with Big Tech results from Microsoft (MSFT), Meta (META), Tesla (TSLA), and Apple (AAPL) headlining the earnings calendar.
+An optim… [+18411 chars]</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
